--- a/data/trans_orig/P0801-Edad-trans_orig.xlsx
+++ b/data/trans_orig/P0801-Edad-trans_orig.xlsx
@@ -538,7 +538,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según limitación a hacer esfuerzos moderados en 2007</t>
+          <t>Población según limitación a hacer esfuerzos moderados en 2007 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>478981</t>
+          <t>478651</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>490440</t>
+          <t>490505</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>96,95%</t>
+          <t>96,88%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>99,27%</t>
+          <t>99,28%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>447578</t>
+          <t>447731</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>461329</t>
+          <t>461679</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>95,74%</t>
+          <t>95,77%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>98,68%</t>
+          <t>98,76%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>931640</t>
+          <t>929661</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>949346</t>
+          <t>949395</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>96,89%</t>
+          <t>96,68%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>98,73%</t>
+          <t>98,74%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>2868</t>
+          <t>2766</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>13834</t>
+          <t>14371</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0,58%</t>
+          <t>0,56%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>2,8%</t>
+          <t>2,91%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>3573</t>
+          <t>3124</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>16128</t>
+          <t>15313</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>0,76%</t>
+          <t>0,67%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>3,45%</t>
+          <t>3,28%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>8600</t>
+          <t>8624</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>24653</t>
+          <t>25620</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>0,89%</t>
+          <t>0,9%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>2,56%</t>
+          <t>2,66%</t>
         </is>
       </c>
     </row>
@@ -964,7 +964,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>5406</t>
+          <t>4803</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -979,7 +979,7 @@
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>1,09%</t>
+          <t>0,97%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -994,12 +994,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>941</t>
+          <t>947</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>9362</t>
+          <t>9393</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1014,7 +1014,7 @@
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>2,0%</t>
+          <t>2,01%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1029,12 +1029,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>1864</t>
+          <t>1816</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>10357</t>
+          <t>11212</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1049,7 +1049,7 @@
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>1,08%</t>
+          <t>1,17%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>702191</t>
+          <t>700501</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>721859</t>
+          <t>721787</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>95,47%</t>
+          <t>95,24%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>98,15%</t>
+          <t>98,14%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>581801</t>
+          <t>582049</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>605496</t>
+          <t>604582</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>93,01%</t>
+          <t>93,05%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>96,8%</t>
+          <t>96,66%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1292381</t>
+          <t>1292369</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1320339</t>
+          <t>1321891</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1279,7 +1279,7 @@
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>97,01%</t>
+          <t>97,13%</t>
         </is>
       </c>
     </row>
@@ -1302,12 +1302,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>9536</t>
+          <t>9074</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>26280</t>
+          <t>26036</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1317,12 +1317,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>1,3%</t>
+          <t>1,23%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>3,57%</t>
+          <t>3,54%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1337,12 +1337,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>17870</t>
+          <t>18121</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>40476</t>
+          <t>40478</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1352,7 +1352,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>2,86%</t>
+          <t>2,9%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1372,12 +1372,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>31836</t>
+          <t>31262</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>58309</t>
+          <t>58946</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1387,12 +1387,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>2,34%</t>
+          <t>2,3%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>4,28%</t>
+          <t>4,33%</t>
         </is>
       </c>
     </row>
@@ -1415,12 +1415,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>2041</t>
+          <t>2406</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>13437</t>
+          <t>13790</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1430,12 +1430,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>0,28%</t>
+          <t>0,33%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>1,83%</t>
+          <t>1,87%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1450,12 +1450,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>933</t>
+          <t>931</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>8427</t>
+          <t>8432</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1485,12 +1485,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>4313</t>
+          <t>4890</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>16911</t>
+          <t>18231</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1500,12 +1500,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>0,32%</t>
+          <t>0,36%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>1,24%</t>
+          <t>1,34%</t>
         </is>
       </c>
     </row>
@@ -1645,12 +1645,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>600482</t>
+          <t>599936</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>620871</t>
+          <t>620579</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1660,12 +1660,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>94,02%</t>
+          <t>93,94%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>97,21%</t>
+          <t>97,17%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1680,12 +1680,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>618295</t>
+          <t>619001</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>646915</t>
+          <t>648653</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1695,12 +1695,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>89,64%</t>
+          <t>89,74%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>93,79%</t>
+          <t>94,04%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1715,12 +1715,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>1224462</t>
+          <t>1228190</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>1262195</t>
+          <t>1262735</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1730,12 +1730,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>92,17%</t>
+          <t>92,46%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>95,02%</t>
+          <t>95,06%</t>
         </is>
       </c>
     </row>
@@ -1758,12 +1758,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>12600</t>
+          <t>12312</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>30898</t>
+          <t>31073</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1773,12 +1773,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>1,97%</t>
+          <t>1,93%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>4,84%</t>
+          <t>4,87%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1793,12 +1793,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>34725</t>
+          <t>33687</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>61538</t>
+          <t>61994</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1808,12 +1808,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>5,03%</t>
+          <t>4,88%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>8,92%</t>
+          <t>8,99%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1828,12 +1828,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>51350</t>
+          <t>52769</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>86377</t>
+          <t>84457</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1843,12 +1843,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>3,87%</t>
+          <t>3,97%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>6,5%</t>
+          <t>6,36%</t>
         </is>
       </c>
     </row>
@@ -1871,12 +1871,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>2643</t>
+          <t>2670</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>12648</t>
+          <t>12022</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1886,12 +1886,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>0,41%</t>
+          <t>0,42%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>1,98%</t>
+          <t>1,88%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1906,12 +1906,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>3921</t>
+          <t>4234</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>16875</t>
+          <t>16121</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1921,12 +1921,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>0,57%</t>
+          <t>0,61%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>2,45%</t>
+          <t>2,34%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1941,12 +1941,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>8765</t>
+          <t>8538</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>24250</t>
+          <t>24795</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1956,12 +1956,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>0,66%</t>
+          <t>0,64%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>1,83%</t>
+          <t>1,87%</t>
         </is>
       </c>
     </row>
@@ -2101,12 +2101,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>467896</t>
+          <t>469830</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>491786</t>
+          <t>492031</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2116,12 +2116,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>90,13%</t>
+          <t>90,5%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>94,73%</t>
+          <t>94,78%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2136,12 +2136,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>418480</t>
+          <t>420361</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>451850</t>
+          <t>453210</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2151,12 +2151,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>81,16%</t>
+          <t>81,52%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>87,63%</t>
+          <t>87,89%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2171,12 +2171,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>897310</t>
+          <t>896713</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>936510</t>
+          <t>937759</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2186,12 +2186,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>86,71%</t>
+          <t>86,66%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>90,5%</t>
+          <t>90,62%</t>
         </is>
       </c>
     </row>
@@ -2214,12 +2214,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>17872</t>
+          <t>17559</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>38154</t>
+          <t>38323</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2229,12 +2229,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>3,44%</t>
+          <t>3,38%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>7,35%</t>
+          <t>7,38%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2249,12 +2249,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>46294</t>
+          <t>47274</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>76678</t>
+          <t>75853</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2264,12 +2264,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>8,98%</t>
+          <t>9,17%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>14,87%</t>
+          <t>14,71%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2284,12 +2284,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>71962</t>
+          <t>70470</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>106251</t>
+          <t>105646</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2299,12 +2299,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>6,95%</t>
+          <t>6,81%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>10,27%</t>
+          <t>10,21%</t>
         </is>
       </c>
     </row>
@@ -2327,12 +2327,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>5855</t>
+          <t>5803</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>19288</t>
+          <t>18704</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2342,12 +2342,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>1,13%</t>
+          <t>1,12%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>3,72%</t>
+          <t>3,6%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2362,12 +2362,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>11414</t>
+          <t>11704</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>29500</t>
+          <t>28668</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2377,12 +2377,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>2,21%</t>
+          <t>2,27%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>5,72%</t>
+          <t>5,56%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2397,12 +2397,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>19759</t>
+          <t>20820</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>41702</t>
+          <t>41518</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2412,12 +2412,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>1,91%</t>
+          <t>2,01%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>4,03%</t>
+          <t>4,01%</t>
         </is>
       </c>
     </row>
@@ -2557,12 +2557,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>291507</t>
+          <t>292004</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>322269</t>
+          <t>323567</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2572,12 +2572,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>75,38%</t>
+          <t>75,51%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>83,34%</t>
+          <t>83,67%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2592,12 +2592,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>274180</t>
+          <t>273160</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>309106</t>
+          <t>308316</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2607,12 +2607,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>67,87%</t>
+          <t>67,62%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>76,51%</t>
+          <t>76,32%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2627,12 +2627,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>573718</t>
+          <t>573222</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>623274</t>
+          <t>621351</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2642,12 +2642,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>72,56%</t>
+          <t>72,5%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>78,83%</t>
+          <t>78,58%</t>
         </is>
       </c>
     </row>
@@ -2670,12 +2670,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>45671</t>
+          <t>46337</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>74481</t>
+          <t>73339</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2685,12 +2685,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>11,81%</t>
+          <t>11,98%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>19,26%</t>
+          <t>18,96%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -2705,12 +2705,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>73664</t>
+          <t>74820</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>106852</t>
+          <t>108457</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2720,12 +2720,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>18,23%</t>
+          <t>18,52%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>26,45%</t>
+          <t>26,85%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2740,12 +2740,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>126263</t>
+          <t>127439</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>170432</t>
+          <t>170974</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2755,12 +2755,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>15,97%</t>
+          <t>16,12%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>21,55%</t>
+          <t>21,62%</t>
         </is>
       </c>
     </row>
@@ -2783,12 +2783,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>13247</t>
+          <t>13107</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>30508</t>
+          <t>31817</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2798,12 +2798,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>3,43%</t>
+          <t>3,39%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>7,89%</t>
+          <t>8,23%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2818,12 +2818,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>13775</t>
+          <t>13977</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>32759</t>
+          <t>31805</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2833,12 +2833,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>3,41%</t>
+          <t>3,46%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>8,11%</t>
+          <t>7,87%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2853,12 +2853,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>31264</t>
+          <t>30514</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>56318</t>
+          <t>58461</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2868,12 +2868,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>3,95%</t>
+          <t>3,86%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>7,12%</t>
+          <t>7,39%</t>
         </is>
       </c>
     </row>
@@ -3013,12 +3013,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>196369</t>
+          <t>196298</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>225978</t>
+          <t>226402</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3028,12 +3028,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>67,12%</t>
+          <t>67,09%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>77,24%</t>
+          <t>77,38%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3048,12 +3048,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>144070</t>
+          <t>144707</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>178632</t>
+          <t>178943</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3063,12 +3063,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>42,01%</t>
+          <t>42,2%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>52,09%</t>
+          <t>52,18%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3083,12 +3083,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>351030</t>
+          <t>346540</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>397751</t>
+          <t>395300</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3098,12 +3098,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>55,24%</t>
+          <t>54,53%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>62,59%</t>
+          <t>62,2%</t>
         </is>
       </c>
     </row>
@@ -3126,12 +3126,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>47060</t>
+          <t>46266</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>72630</t>
+          <t>74247</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3141,12 +3141,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>16,08%</t>
+          <t>15,81%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>24,82%</t>
+          <t>25,38%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3161,12 +3161,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>122609</t>
+          <t>122161</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>156709</t>
+          <t>156025</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3176,12 +3176,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>35,75%</t>
+          <t>35,62%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>45,7%</t>
+          <t>45,5%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3196,12 +3196,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>173019</t>
+          <t>176906</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>218096</t>
+          <t>222696</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3211,12 +3211,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>27,22%</t>
+          <t>27,84%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>34,32%</t>
+          <t>35,04%</t>
         </is>
       </c>
     </row>
@@ -3239,12 +3239,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>12762</t>
+          <t>13395</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>29934</t>
+          <t>30922</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3254,12 +3254,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>4,36%</t>
+          <t>4,58%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>10,23%</t>
+          <t>10,57%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3274,12 +3274,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>32636</t>
+          <t>31803</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>55363</t>
+          <t>55578</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3289,12 +3289,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>9,52%</t>
+          <t>9,27%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>16,14%</t>
+          <t>16,21%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3309,12 +3309,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>50887</t>
+          <t>49587</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>79613</t>
+          <t>79285</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3324,12 +3324,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>8,01%</t>
+          <t>7,8%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>12,53%</t>
+          <t>12,48%</t>
         </is>
       </c>
     </row>
@@ -3469,12 +3469,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>83808</t>
+          <t>84668</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>112198</t>
+          <t>112318</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3484,12 +3484,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>39,93%</t>
+          <t>40,34%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>53,46%</t>
+          <t>53,51%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3504,12 +3504,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>63708</t>
+          <t>65794</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>97616</t>
+          <t>98150</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3519,12 +3519,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>19,08%</t>
+          <t>19,7%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>29,23%</t>
+          <t>29,39%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3539,12 +3539,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>156915</t>
+          <t>158033</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>201176</t>
+          <t>203367</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3554,12 +3554,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>28,86%</t>
+          <t>29,06%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>37,0%</t>
+          <t>37,4%</t>
         </is>
       </c>
     </row>
@@ -3582,12 +3582,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>64175</t>
+          <t>62615</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>90371</t>
+          <t>90824</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3597,12 +3597,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>30,58%</t>
+          <t>29,83%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>43,06%</t>
+          <t>43,27%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3617,12 +3617,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>147895</t>
+          <t>149229</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>186570</t>
+          <t>187522</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3632,12 +3632,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>44,29%</t>
+          <t>44,69%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>55,87%</t>
+          <t>56,16%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3652,12 +3652,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>220427</t>
+          <t>221863</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>267766</t>
+          <t>268364</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3667,12 +3667,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>40,54%</t>
+          <t>40,8%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>49,24%</t>
+          <t>49,35%</t>
         </is>
       </c>
     </row>
@@ -3695,12 +3695,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>25850</t>
+          <t>26342</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>48056</t>
+          <t>47158</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -3710,12 +3710,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>12,32%</t>
+          <t>12,55%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>22,9%</t>
+          <t>22,47%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -3730,12 +3730,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>68563</t>
+          <t>68679</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>101662</t>
+          <t>102986</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -3745,12 +3745,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>20,53%</t>
+          <t>20,57%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>30,45%</t>
+          <t>30,84%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3765,12 +3765,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>101254</t>
+          <t>101276</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>142687</t>
+          <t>140063</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -3785,7 +3785,7 @@
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>26,24%</t>
+          <t>25,76%</t>
         </is>
       </c>
     </row>
@@ -3925,12 +3925,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>2876172</t>
+          <t>2876209</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>2943079</t>
+          <t>2946110</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -3945,7 +3945,7 @@
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>89,82%</t>
+          <t>89,92%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -3960,12 +3960,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>2603467</t>
+          <t>2605295</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>2703467</t>
+          <t>2701280</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -3975,12 +3975,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>77,04%</t>
+          <t>77,1%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>80,0%</t>
+          <t>79,94%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -3995,12 +3995,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>5500015</t>
+          <t>5510525</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>5624881</t>
+          <t>5624915</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -4010,7 +4010,7 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>82,64%</t>
+          <t>82,79%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
@@ -4038,12 +4038,12 @@
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>235373</t>
+          <t>233979</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>294119</t>
+          <t>294603</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
@@ -4053,12 +4053,12 @@
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>7,18%</t>
+          <t>7,14%</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>8,98%</t>
+          <t>8,99%</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
@@ -4073,12 +4073,12 @@
       </c>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>499517</t>
+          <t>501078</t>
         </is>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>582911</t>
+          <t>587800</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
@@ -4088,12 +4088,12 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>14,78%</t>
+          <t>14,83%</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
         <is>
-          <t>17,25%</t>
+          <t>17,39%</t>
         </is>
       </c>
       <c r="Q33" s="2" t="inlineStr">
@@ -4108,12 +4108,12 @@
       </c>
       <c r="S33" s="2" t="inlineStr">
         <is>
-          <t>751247</t>
+          <t>751730</t>
         </is>
       </c>
       <c r="T33" s="2" t="inlineStr">
         <is>
-          <t>859559</t>
+          <t>855295</t>
         </is>
       </c>
       <c r="U33" s="2" t="inlineStr">
@@ -4128,7 +4128,7 @@
       </c>
       <c r="W33" s="2" t="inlineStr">
         <is>
-          <t>12,91%</t>
+          <t>12,85%</t>
         </is>
       </c>
     </row>
@@ -4151,12 +4151,12 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>83807</t>
+          <t>84180</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>120021</t>
+          <t>124806</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -4166,12 +4166,12 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>2,56%</t>
+          <t>2,57%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>3,66%</t>
+          <t>3,81%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -4186,12 +4186,12 @@
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>158379</t>
+          <t>156249</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>211446</t>
+          <t>209051</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -4201,12 +4201,12 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>4,69%</t>
+          <t>4,62%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>6,26%</t>
+          <t>6,19%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -4221,12 +4221,12 @@
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>250157</t>
+          <t>252141</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>316877</t>
+          <t>317893</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -4236,12 +4236,12 @@
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>3,76%</t>
+          <t>3,79%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>4,76%</t>
+          <t>4,78%</t>
         </is>
       </c>
     </row>
@@ -4421,7 +4421,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según limitación a hacer esfuerzos moderados en 2012</t>
+          <t>Población según limitación a hacer esfuerzos moderados en 2012 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -4616,12 +4616,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>438335</t>
+          <t>439073</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>450562</t>
+          <t>450478</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -4631,12 +4631,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>96,52%</t>
+          <t>96,68%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>99,21%</t>
+          <t>99,19%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -4651,12 +4651,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>406613</t>
+          <t>405597</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>421752</t>
+          <t>421670</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -4666,12 +4666,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>94,51%</t>
+          <t>94,27%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>98,03%</t>
+          <t>98,01%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4686,12 +4686,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>851269</t>
+          <t>849679</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>870068</t>
+          <t>869829</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4701,12 +4701,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>96,26%</t>
+          <t>96,08%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>98,38%</t>
+          <t>98,36%</t>
         </is>
       </c>
     </row>
@@ -4729,12 +4729,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>2894</t>
+          <t>2973</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>14781</t>
+          <t>14082</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4744,12 +4744,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0,64%</t>
+          <t>0,65%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>3,25%</t>
+          <t>3,1%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4764,12 +4764,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>4918</t>
+          <t>4899</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>17279</t>
+          <t>18447</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4784,7 +4784,7 @@
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>4,02%</t>
+          <t>4,29%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4799,12 +4799,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>9283</t>
+          <t>10121</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>26227</t>
+          <t>28152</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4814,12 +4814,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>1,05%</t>
+          <t>1,14%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>2,97%</t>
+          <t>3,18%</t>
         </is>
       </c>
     </row>
@@ -4847,7 +4847,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>4360</t>
+          <t>4345</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -4877,12 +4877,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>1883</t>
+          <t>1907</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>10946</t>
+          <t>11042</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -4897,7 +4897,7 @@
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>2,54%</t>
+          <t>2,57%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -4912,12 +4912,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>1914</t>
+          <t>2007</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>12145</t>
+          <t>11781</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -4927,12 +4927,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>0,22%</t>
+          <t>0,23%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>1,37%</t>
+          <t>1,33%</t>
         </is>
       </c>
     </row>
@@ -5072,12 +5072,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>651249</t>
+          <t>651446</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>671846</t>
+          <t>671286</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -5087,12 +5087,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>94,78%</t>
+          <t>94,81%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>97,78%</t>
+          <t>97,7%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -5107,12 +5107,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>570001</t>
+          <t>569311</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>591637</t>
+          <t>591462</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -5122,12 +5122,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>93,4%</t>
+          <t>93,29%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>96,95%</t>
+          <t>96,92%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -5142,12 +5142,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1228533</t>
+          <t>1229302</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1258362</t>
+          <t>1257980</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -5157,12 +5157,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>94,7%</t>
+          <t>94,76%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>97,0%</t>
+          <t>96,97%</t>
         </is>
       </c>
     </row>
@@ -5185,12 +5185,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>10802</t>
+          <t>11358</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>29374</t>
+          <t>28651</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -5200,12 +5200,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>1,57%</t>
+          <t>1,65%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>4,28%</t>
+          <t>4,17%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -5220,12 +5220,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>17592</t>
+          <t>17860</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>38929</t>
+          <t>39951</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -5235,12 +5235,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>2,88%</t>
+          <t>2,93%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>6,38%</t>
+          <t>6,55%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -5255,12 +5255,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>33376</t>
+          <t>34475</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>61172</t>
+          <t>60230</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -5270,12 +5270,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>2,57%</t>
+          <t>2,66%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>4,72%</t>
+          <t>4,64%</t>
         </is>
       </c>
     </row>
@@ -5298,12 +5298,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>1862</t>
+          <t>1894</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>13332</t>
+          <t>14197</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -5313,12 +5313,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>0,27%</t>
+          <t>0,28%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>1,94%</t>
+          <t>2,07%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -5338,7 +5338,7 @@
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>6258</t>
+          <t>5229</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -5353,7 +5353,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>1,03%</t>
+          <t>0,86%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -5368,12 +5368,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>2747</t>
+          <t>2817</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>15665</t>
+          <t>14911</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -5383,12 +5383,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>0,21%</t>
+          <t>0,22%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>1,21%</t>
+          <t>1,15%</t>
         </is>
       </c>
     </row>
@@ -5528,12 +5528,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>624927</t>
+          <t>627063</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>651526</t>
+          <t>651996</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -5543,12 +5543,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>91,65%</t>
+          <t>91,96%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>95,55%</t>
+          <t>95,62%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -5563,12 +5563,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>610845</t>
+          <t>612381</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>646022</t>
+          <t>646783</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -5578,12 +5578,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>85,93%</t>
+          <t>86,15%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>90,88%</t>
+          <t>90,99%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -5598,12 +5598,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>1244836</t>
+          <t>1247974</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>1291388</t>
+          <t>1291511</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -5613,12 +5613,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>89,38%</t>
+          <t>89,61%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>92,72%</t>
+          <t>92,73%</t>
         </is>
       </c>
     </row>
@@ -5641,12 +5641,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>20579</t>
+          <t>20093</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>42206</t>
+          <t>40978</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -5656,12 +5656,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>3,02%</t>
+          <t>2,95%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>6,19%</t>
+          <t>6,01%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5676,12 +5676,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>48636</t>
+          <t>48308</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>78566</t>
+          <t>79430</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5691,12 +5691,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>6,84%</t>
+          <t>6,8%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>11,05%</t>
+          <t>11,17%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5711,12 +5711,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>74078</t>
+          <t>74383</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>113635</t>
+          <t>115979</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5726,12 +5726,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>5,32%</t>
+          <t>5,34%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>8,16%</t>
+          <t>8,33%</t>
         </is>
       </c>
     </row>
@@ -5754,12 +5754,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>6115</t>
+          <t>6654</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>21522</t>
+          <t>21290</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5769,12 +5769,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>0,9%</t>
+          <t>0,98%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>3,16%</t>
+          <t>3,12%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5789,12 +5789,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>10672</t>
+          <t>10501</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>29598</t>
+          <t>28578</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5804,12 +5804,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>1,5%</t>
+          <t>1,48%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>4,16%</t>
+          <t>4,02%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5824,12 +5824,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>19785</t>
+          <t>20127</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>42728</t>
+          <t>43332</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5839,12 +5839,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>1,42%</t>
+          <t>1,45%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>3,07%</t>
+          <t>3,11%</t>
         </is>
       </c>
     </row>
@@ -5984,12 +5984,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>529585</t>
+          <t>530630</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>561408</t>
+          <t>562205</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -5999,12 +5999,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>86,17%</t>
+          <t>86,33%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>91,34%</t>
+          <t>91,47%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -6019,12 +6019,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>493294</t>
+          <t>493955</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>532369</t>
+          <t>530846</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -6034,12 +6034,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>80,05%</t>
+          <t>80,16%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>86,4%</t>
+          <t>86,15%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -6054,12 +6054,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>1036143</t>
+          <t>1035686</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>1084619</t>
+          <t>1084715</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -6069,12 +6069,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>84,18%</t>
+          <t>84,15%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>88,12%</t>
+          <t>88,13%</t>
         </is>
       </c>
     </row>
@@ -6097,12 +6097,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>40139</t>
+          <t>40175</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>69612</t>
+          <t>68088</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -6112,12 +6112,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>6,53%</t>
+          <t>6,54%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>11,33%</t>
+          <t>11,08%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -6132,12 +6132,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>63825</t>
+          <t>64179</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>98972</t>
+          <t>97330</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -6147,12 +6147,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>10,36%</t>
+          <t>10,42%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>16,06%</t>
+          <t>15,8%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -6167,12 +6167,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>111611</t>
+          <t>110569</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>156435</t>
+          <t>155693</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -6182,12 +6182,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>9,07%</t>
+          <t>8,98%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>12,71%</t>
+          <t>12,65%</t>
         </is>
       </c>
     </row>
@@ -6210,12 +6210,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>8059</t>
+          <t>8214</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>22895</t>
+          <t>23475</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -6225,12 +6225,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>1,31%</t>
+          <t>1,34%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>3,73%</t>
+          <t>3,82%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -6245,12 +6245,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>14707</t>
+          <t>14745</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>35045</t>
+          <t>34960</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -6265,7 +6265,7 @@
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>5,69%</t>
+          <t>5,67%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -6280,12 +6280,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>25651</t>
+          <t>26506</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>52029</t>
+          <t>50311</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -6295,12 +6295,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>2,08%</t>
+          <t>2,15%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>4,23%</t>
+          <t>4,09%</t>
         </is>
       </c>
     </row>
@@ -6440,12 +6440,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>326437</t>
+          <t>327339</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>360889</t>
+          <t>361152</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -6455,12 +6455,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>76,02%</t>
+          <t>76,23%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>84,04%</t>
+          <t>84,1%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -6475,12 +6475,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>258233</t>
+          <t>258459</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>301281</t>
+          <t>300537</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -6490,12 +6490,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>57,67%</t>
+          <t>57,72%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>67,28%</t>
+          <t>67,11%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -6510,12 +6510,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>597487</t>
+          <t>598987</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>651355</t>
+          <t>656093</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -6525,12 +6525,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>68,11%</t>
+          <t>68,28%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>74,25%</t>
+          <t>74,79%</t>
         </is>
       </c>
     </row>
@@ -6553,12 +6553,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>43999</t>
+          <t>44294</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>73466</t>
+          <t>75785</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -6568,12 +6568,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>10,25%</t>
+          <t>10,31%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>17,11%</t>
+          <t>17,65%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -6588,12 +6588,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>101917</t>
+          <t>103442</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>140160</t>
+          <t>140025</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -6603,12 +6603,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>22,76%</t>
+          <t>23,1%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>31,3%</t>
+          <t>31,27%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -6623,12 +6623,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>156533</t>
+          <t>153391</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>205573</t>
+          <t>201506</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -6638,12 +6638,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>17,84%</t>
+          <t>17,49%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>23,43%</t>
+          <t>22,97%</t>
         </is>
       </c>
     </row>
@@ -6666,12 +6666,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>17450</t>
+          <t>18139</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>38827</t>
+          <t>39422</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -6681,12 +6681,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>4,06%</t>
+          <t>4,22%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>9,04%</t>
+          <t>9,18%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -6701,12 +6701,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>35033</t>
+          <t>35842</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>63107</t>
+          <t>62714</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -6716,12 +6716,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>7,82%</t>
+          <t>8,0%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>14,09%</t>
+          <t>14,0%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -6736,12 +6736,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>58351</t>
+          <t>58369</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>91740</t>
+          <t>92418</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -6756,7 +6756,7 @@
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>10,46%</t>
+          <t>10,54%</t>
         </is>
       </c>
     </row>
@@ -6896,12 +6896,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>183201</t>
+          <t>182899</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>218141</t>
+          <t>219882</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -6911,12 +6911,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>59,14%</t>
+          <t>59,04%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>70,42%</t>
+          <t>70,98%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -6931,12 +6931,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>141432</t>
+          <t>140735</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>177564</t>
+          <t>179216</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -6946,12 +6946,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>39,95%</t>
+          <t>39,76%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>50,16%</t>
+          <t>50,63%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -6966,12 +6966,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>337437</t>
+          <t>338205</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>389011</t>
+          <t>390553</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -6981,12 +6981,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>50,84%</t>
+          <t>50,95%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>58,61%</t>
+          <t>58,84%</t>
         </is>
       </c>
     </row>
@@ -7009,12 +7009,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>55993</t>
+          <t>56458</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>89299</t>
+          <t>88695</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -7024,12 +7024,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>18,07%</t>
+          <t>18,22%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>28,83%</t>
+          <t>28,63%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -7044,12 +7044,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>108501</t>
+          <t>107779</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>143835</t>
+          <t>143142</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -7059,12 +7059,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>30,65%</t>
+          <t>30,45%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>40,63%</t>
+          <t>40,44%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -7079,12 +7079,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>173169</t>
+          <t>174826</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>222179</t>
+          <t>220602</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -7094,12 +7094,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>26,09%</t>
+          <t>26,34%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>33,47%</t>
+          <t>33,23%</t>
         </is>
       </c>
     </row>
@@ -7122,12 +7122,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>25454</t>
+          <t>25439</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>49839</t>
+          <t>50352</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -7137,12 +7137,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>8,22%</t>
+          <t>8,21%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>16,09%</t>
+          <t>16,25%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -7157,12 +7157,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>54094</t>
+          <t>55473</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>84702</t>
+          <t>84079</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -7172,12 +7172,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>15,28%</t>
+          <t>15,67%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>23,93%</t>
+          <t>23,75%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -7192,12 +7192,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>85924</t>
+          <t>86726</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>126157</t>
+          <t>122059</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -7207,12 +7207,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>12,94%</t>
+          <t>13,07%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>19,01%</t>
+          <t>18,39%</t>
         </is>
       </c>
     </row>
@@ -7352,12 +7352,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>67034</t>
+          <t>66048</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>96786</t>
+          <t>97722</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -7367,12 +7367,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>26,83%</t>
+          <t>26,44%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>38,74%</t>
+          <t>39,11%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -7387,12 +7387,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>59680</t>
+          <t>58749</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>92133</t>
+          <t>90356</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -7402,12 +7402,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>15,34%</t>
+          <t>15,1%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>23,69%</t>
+          <t>23,23%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -7422,12 +7422,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>131554</t>
+          <t>133830</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>178541</t>
+          <t>180157</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -7437,12 +7437,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>20,59%</t>
+          <t>20,95%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>27,95%</t>
+          <t>28,2%</t>
         </is>
       </c>
     </row>
@@ -7465,12 +7465,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>80647</t>
+          <t>80142</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>113954</t>
+          <t>113713</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -7480,12 +7480,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>32,28%</t>
+          <t>32,08%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>45,61%</t>
+          <t>45,51%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -7500,12 +7500,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>135726</t>
+          <t>136663</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>175710</t>
+          <t>176992</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -7515,12 +7515,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>34,89%</t>
+          <t>35,13%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>45,17%</t>
+          <t>45,5%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -7535,12 +7535,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>227148</t>
+          <t>225791</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>279365</t>
+          <t>280723</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -7550,12 +7550,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>35,56%</t>
+          <t>35,34%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>43,73%</t>
+          <t>43,94%</t>
         </is>
       </c>
     </row>
@@ -7578,12 +7578,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>56352</t>
+          <t>56302</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>87668</t>
+          <t>89066</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -7593,12 +7593,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>22,55%</t>
+          <t>22,53%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>35,09%</t>
+          <t>35,65%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -7613,12 +7613,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>140996</t>
+          <t>140562</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>180953</t>
+          <t>181201</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -7628,12 +7628,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>36,25%</t>
+          <t>36,14%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>46,52%</t>
+          <t>46,58%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -7648,12 +7648,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>208434</t>
+          <t>205843</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>258459</t>
+          <t>259968</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -7663,12 +7663,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>32,63%</t>
+          <t>32,22%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>40,46%</t>
+          <t>40,69%</t>
         </is>
       </c>
     </row>
@@ -7808,12 +7808,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>2881909</t>
+          <t>2881731</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>2967223</t>
+          <t>2967405</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -7823,7 +7823,7 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>84,1%</t>
+          <t>84,09%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
@@ -7843,12 +7843,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>2603398</t>
+          <t>2608515</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>2709062</t>
+          <t>2712998</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -7858,12 +7858,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>73,16%</t>
+          <t>73,31%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>76,13%</t>
+          <t>76,24%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -7878,12 +7878,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>5504372</t>
+          <t>5513816</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>5646540</t>
+          <t>5647275</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -7893,12 +7893,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>78,8%</t>
+          <t>78,94%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>80,84%</t>
+          <t>80,85%</t>
         </is>
       </c>
     </row>
@@ -7921,12 +7921,12 @@
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>301580</t>
+          <t>299585</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>369805</t>
+          <t>371052</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
@@ -7936,12 +7936,12 @@
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>8,8%</t>
+          <t>8,74%</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>10,79%</t>
+          <t>10,83%</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
@@ -7956,12 +7956,12 @@
       </c>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>535995</t>
+          <t>534866</t>
         </is>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>626076</t>
+          <t>625028</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
@@ -7971,12 +7971,12 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>15,06%</t>
+          <t>15,03%</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
         <is>
-          <t>17,59%</t>
+          <t>17,57%</t>
         </is>
       </c>
       <c r="Q33" s="2" t="inlineStr">
@@ -7991,12 +7991,12 @@
       </c>
       <c r="S33" s="2" t="inlineStr">
         <is>
-          <t>857992</t>
+          <t>855193</t>
         </is>
       </c>
       <c r="T33" s="2" t="inlineStr">
         <is>
-          <t>977917</t>
+          <t>975111</t>
         </is>
       </c>
       <c r="U33" s="2" t="inlineStr">
@@ -8006,12 +8006,12 @@
       </c>
       <c r="V33" s="2" t="inlineStr">
         <is>
-          <t>12,28%</t>
+          <t>12,24%</t>
         </is>
       </c>
       <c r="W33" s="2" t="inlineStr">
         <is>
-          <t>14,0%</t>
+          <t>13,96%</t>
         </is>
       </c>
     </row>
@@ -8034,12 +8034,12 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>139269</t>
+          <t>141356</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>192022</t>
+          <t>194331</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -8049,12 +8049,12 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>4,06%</t>
+          <t>4,13%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>5,6%</t>
+          <t>5,67%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -8069,12 +8069,12 @@
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>287872</t>
+          <t>286207</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>355099</t>
+          <t>356685</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -8084,12 +8084,12 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>8,09%</t>
+          <t>8,04%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>9,98%</t>
+          <t>10,02%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -8104,12 +8104,12 @@
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>442895</t>
+          <t>443843</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>533913</t>
+          <t>531141</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -8119,12 +8119,12 @@
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>6,34%</t>
+          <t>6,35%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>7,64%</t>
+          <t>7,6%</t>
         </is>
       </c>
     </row>
@@ -8304,7 +8304,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según limitación a hacer esfuerzos moderados en 2016</t>
+          <t>Población según limitación a hacer esfuerzos moderados en 2016 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -8499,7 +8499,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>410941</t>
+          <t>411450</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -8514,7 +8514,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>97,97%</t>
+          <t>98,09%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -8534,12 +8534,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>375805</t>
+          <t>375791</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>388970</t>
+          <t>389213</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -8554,7 +8554,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>98,29%</t>
+          <t>98,35%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -8569,12 +8569,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>791414</t>
+          <t>792426</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>806787</t>
+          <t>806848</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -8584,7 +8584,7 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>97,08%</t>
+          <t>97,2%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
@@ -8617,7 +8617,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>8522</t>
+          <t>8013</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -8632,7 +8632,7 @@
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>2,03%</t>
+          <t>1,91%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -8647,12 +8647,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>5787</t>
+          <t>5645</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>18788</t>
+          <t>18673</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -8662,12 +8662,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>1,46%</t>
+          <t>1,43%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>4,75%</t>
+          <t>4,72%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -8682,12 +8682,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>7573</t>
+          <t>7448</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>22471</t>
+          <t>21271</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -8697,12 +8697,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>0,93%</t>
+          <t>0,91%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>2,76%</t>
+          <t>2,61%</t>
         </is>
       </c>
     </row>
@@ -8725,97 +8725,97 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K6" s="2" t="inlineStr">
+        <is>
+          <t>1026</t>
+        </is>
+      </c>
+      <c r="L6" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>2044</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
+      <c r="M6" s="2" t="inlineStr">
+        <is>
+          <t>5788</t>
+        </is>
+      </c>
+      <c r="N6" s="2" t="inlineStr">
+        <is>
+          <t>0,26%</t>
+        </is>
+      </c>
+      <c r="O6" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>0,49%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
+      <c r="P6" s="2" t="inlineStr">
+        <is>
+          <t>1,46%</t>
+        </is>
+      </c>
+      <c r="Q6" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="K6" s="2" t="inlineStr">
+      <c r="R6" s="2" t="inlineStr">
         <is>
           <t>1026</t>
         </is>
       </c>
-      <c r="L6" s="2" t="inlineStr">
+      <c r="S6" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>5177</t>
-        </is>
-      </c>
-      <c r="N6" s="2" t="inlineStr">
-        <is>
-          <t>0,26%</t>
-        </is>
-      </c>
-      <c r="O6" s="2" t="inlineStr">
+      <c r="T6" s="2" t="inlineStr">
+        <is>
+          <t>5802</t>
+        </is>
+      </c>
+      <c r="U6" s="2" t="inlineStr">
+        <is>
+          <t>0,13%</t>
+        </is>
+      </c>
+      <c r="V6" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P6" s="2" t="inlineStr">
-        <is>
-          <t>1,31%</t>
-        </is>
-      </c>
-      <c r="Q6" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R6" s="2" t="inlineStr">
-        <is>
-          <t>1026</t>
-        </is>
-      </c>
-      <c r="S6" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T6" s="2" t="inlineStr">
-        <is>
-          <t>5134</t>
-        </is>
-      </c>
-      <c r="U6" s="2" t="inlineStr">
-        <is>
-          <t>0,13%</t>
-        </is>
-      </c>
-      <c r="V6" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>0,63%</t>
+          <t>0,71%</t>
         </is>
       </c>
     </row>
@@ -8955,12 +8955,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>559388</t>
+          <t>559479</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>577781</t>
+          <t>578337</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -8970,82 +8970,82 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
+          <t>94,75%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>97,94%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
+          <t>554</t>
+        </is>
+      </c>
+      <c r="K8" s="2" t="inlineStr">
+        <is>
+          <t>538224</t>
+        </is>
+      </c>
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>525382</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>546340</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
+        <is>
+          <t>95,51%</t>
+        </is>
+      </c>
+      <c r="O8" s="2" t="inlineStr">
+        <is>
+          <t>93,23%</t>
+        </is>
+      </c>
+      <c r="P8" s="2" t="inlineStr">
+        <is>
+          <t>96,95%</t>
+        </is>
+      </c>
+      <c r="Q8" s="2" t="inlineStr">
+        <is>
+          <t>1103</t>
+        </is>
+      </c>
+      <c r="R8" s="2" t="inlineStr">
+        <is>
+          <t>1108532</t>
+        </is>
+      </c>
+      <c r="S8" s="2" t="inlineStr">
+        <is>
+          <t>1093209</t>
+        </is>
+      </c>
+      <c r="T8" s="2" t="inlineStr">
+        <is>
+          <t>1120870</t>
+        </is>
+      </c>
+      <c r="U8" s="2" t="inlineStr">
+        <is>
+          <t>96,06%</t>
+        </is>
+      </c>
+      <c r="V8" s="2" t="inlineStr">
+        <is>
           <t>94,73%</t>
         </is>
       </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>97,85%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>554</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>538224</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>526358</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>546666</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>95,51%</t>
-        </is>
-      </c>
-      <c r="O8" s="2" t="inlineStr">
-        <is>
-          <t>93,4%</t>
-        </is>
-      </c>
-      <c r="P8" s="2" t="inlineStr">
-        <is>
-          <t>97,01%</t>
-        </is>
-      </c>
-      <c r="Q8" s="2" t="inlineStr">
-        <is>
-          <t>1103</t>
-        </is>
-      </c>
-      <c r="R8" s="2" t="inlineStr">
-        <is>
-          <t>1108532</t>
-        </is>
-      </c>
-      <c r="S8" s="2" t="inlineStr">
-        <is>
-          <t>1092201</t>
-        </is>
-      </c>
-      <c r="T8" s="2" t="inlineStr">
-        <is>
-          <t>1119944</t>
-        </is>
-      </c>
-      <c r="U8" s="2" t="inlineStr">
-        <is>
-          <t>96,06%</t>
-        </is>
-      </c>
-      <c r="V8" s="2" t="inlineStr">
-        <is>
-          <t>94,64%</t>
-        </is>
-      </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>97,05%</t>
+          <t>97,13%</t>
         </is>
       </c>
     </row>
@@ -9068,12 +9068,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>7433</t>
+          <t>7585</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>24296</t>
+          <t>23685</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -9083,12 +9083,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>1,26%</t>
+          <t>1,28%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>4,11%</t>
+          <t>4,01%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -9103,12 +9103,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>8915</t>
+          <t>9524</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>25151</t>
+          <t>25460</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -9118,12 +9118,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>1,58%</t>
+          <t>1,69%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>4,46%</t>
+          <t>4,52%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -9138,12 +9138,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>20751</t>
+          <t>20686</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>44005</t>
+          <t>43597</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -9153,12 +9153,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>1,8%</t>
+          <t>1,79%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>3,81%</t>
+          <t>3,78%</t>
         </is>
       </c>
     </row>
@@ -9181,12 +9181,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>2012</t>
+          <t>1992</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>12005</t>
+          <t>12780</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -9201,7 +9201,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>2,03%</t>
+          <t>2,16%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -9216,12 +9216,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>4248</t>
+          <t>4675</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>17865</t>
+          <t>17448</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -9231,12 +9231,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>0,75%</t>
+          <t>0,83%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>3,17%</t>
+          <t>3,1%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -9251,12 +9251,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>9106</t>
+          <t>8867</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>25087</t>
+          <t>25384</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -9266,12 +9266,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>0,79%</t>
+          <t>0,77%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>2,17%</t>
+          <t>2,2%</t>
         </is>
       </c>
     </row>
@@ -9411,12 +9411,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>621266</t>
+          <t>620209</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>644312</t>
+          <t>644244</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -9426,12 +9426,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>92,85%</t>
+          <t>92,69%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>96,3%</t>
+          <t>96,29%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -9446,12 +9446,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>597042</t>
+          <t>597038</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>623608</t>
+          <t>624715</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -9466,7 +9466,7 @@
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>94,29%</t>
+          <t>94,46%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -9481,12 +9481,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>1225751</t>
+          <t>1227117</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>1264079</t>
+          <t>1263112</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -9496,12 +9496,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>92,13%</t>
+          <t>92,23%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>95,01%</t>
+          <t>94,94%</t>
         </is>
       </c>
     </row>
@@ -9524,12 +9524,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>18874</t>
+          <t>18364</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>41813</t>
+          <t>39699</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -9539,12 +9539,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>2,82%</t>
+          <t>2,74%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>6,25%</t>
+          <t>5,93%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -9559,12 +9559,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>30690</t>
+          <t>28986</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>55559</t>
+          <t>55222</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -9574,12 +9574,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>4,64%</t>
+          <t>4,38%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>8,4%</t>
+          <t>8,35%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -9594,12 +9594,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>51781</t>
+          <t>53290</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>86736</t>
+          <t>86166</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -9609,12 +9609,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>3,89%</t>
+          <t>4,01%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>6,52%</t>
+          <t>6,48%</t>
         </is>
       </c>
     </row>
@@ -9637,12 +9637,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>2982</t>
+          <t>3030</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>14368</t>
+          <t>14615</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -9657,7 +9657,7 @@
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>2,15%</t>
+          <t>2,18%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -9672,12 +9672,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>4344</t>
+          <t>3804</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>16473</t>
+          <t>15709</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -9687,12 +9687,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>0,66%</t>
+          <t>0,58%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>2,49%</t>
+          <t>2,38%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -9707,12 +9707,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>9385</t>
+          <t>9391</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>24887</t>
+          <t>24563</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -9727,7 +9727,7 @@
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>1,87%</t>
+          <t>1,85%</t>
         </is>
       </c>
     </row>
@@ -9867,12 +9867,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>551386</t>
+          <t>552140</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>586334</t>
+          <t>585430</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -9882,12 +9882,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>85,35%</t>
+          <t>85,46%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>90,76%</t>
+          <t>90,62%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -9902,12 +9902,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>524930</t>
+          <t>528984</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>564610</t>
+          <t>565849</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -9917,12 +9917,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>80,87%</t>
+          <t>81,5%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>86,99%</t>
+          <t>87,18%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -9937,12 +9937,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>1094162</t>
+          <t>1092113</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>1142253</t>
+          <t>1142919</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -9952,12 +9952,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>84,48%</t>
+          <t>84,32%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>88,2%</t>
+          <t>88,25%</t>
         </is>
       </c>
     </row>
@@ -9980,12 +9980,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>35196</t>
+          <t>35567</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>64084</t>
+          <t>64028</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -9995,12 +9995,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>5,45%</t>
+          <t>5,51%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>9,92%</t>
+          <t>9,91%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -10015,12 +10015,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>48659</t>
+          <t>48481</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>79798</t>
+          <t>78929</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -10030,12 +10030,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>7,5%</t>
+          <t>7,47%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>12,29%</t>
+          <t>12,16%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -10050,12 +10050,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>92042</t>
+          <t>91557</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>131710</t>
+          <t>132440</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -10065,12 +10065,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>7,11%</t>
+          <t>7,07%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>10,17%</t>
+          <t>10,23%</t>
         </is>
       </c>
     </row>
@@ -10093,12 +10093,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>17895</t>
+          <t>17934</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>40576</t>
+          <t>38931</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -10108,12 +10108,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>2,77%</t>
+          <t>2,78%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>6,28%</t>
+          <t>6,03%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -10128,12 +10128,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>27638</t>
+          <t>28765</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>53513</t>
+          <t>54036</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -10143,12 +10143,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>4,26%</t>
+          <t>4,43%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>8,24%</t>
+          <t>8,32%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -10163,12 +10163,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>52451</t>
+          <t>51032</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>84249</t>
+          <t>83902</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -10178,12 +10178,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>4,05%</t>
+          <t>3,94%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>6,51%</t>
+          <t>6,48%</t>
         </is>
       </c>
     </row>
@@ -10323,12 +10323,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>365467</t>
+          <t>365871</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>402478</t>
+          <t>403579</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -10338,12 +10338,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>76,47%</t>
+          <t>76,56%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>84,21%</t>
+          <t>84,45%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -10358,12 +10358,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>316781</t>
+          <t>315966</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>360227</t>
+          <t>359902</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -10373,12 +10373,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>63,76%</t>
+          <t>63,59%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>72,5%</t>
+          <t>72,44%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -10393,12 +10393,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>693386</t>
+          <t>698452</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>753921</t>
+          <t>755955</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -10408,12 +10408,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>71,13%</t>
+          <t>71,65%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>77,34%</t>
+          <t>77,55%</t>
         </is>
       </c>
     </row>
@@ -10436,12 +10436,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>53244</t>
+          <t>52282</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>84234</t>
+          <t>84648</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -10451,12 +10451,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>11,14%</t>
+          <t>10,94%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>17,63%</t>
+          <t>17,71%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -10471,12 +10471,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>83986</t>
+          <t>83448</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>119068</t>
+          <t>119315</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -10486,12 +10486,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>16,9%</t>
+          <t>16,8%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>23,96%</t>
+          <t>24,01%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -10506,12 +10506,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>144629</t>
+          <t>145841</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>194656</t>
+          <t>195360</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -10521,12 +10521,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>14,84%</t>
+          <t>14,96%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>19,97%</t>
+          <t>20,04%</t>
         </is>
       </c>
     </row>
@@ -10549,12 +10549,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>15923</t>
+          <t>14418</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>36690</t>
+          <t>37400</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -10564,12 +10564,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>3,33%</t>
+          <t>3,02%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>7,68%</t>
+          <t>7,83%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -10584,12 +10584,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>43043</t>
+          <t>42954</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>72190</t>
+          <t>72813</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -10599,12 +10599,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>8,66%</t>
+          <t>8,65%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>14,53%</t>
+          <t>14,65%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -10619,12 +10619,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>63277</t>
+          <t>63486</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>100769</t>
+          <t>103127</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -10634,12 +10634,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>6,49%</t>
+          <t>6,51%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>10,34%</t>
+          <t>10,58%</t>
         </is>
       </c>
     </row>
@@ -10779,12 +10779,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>213399</t>
+          <t>215014</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>246046</t>
+          <t>248229</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -10794,12 +10794,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>63,83%</t>
+          <t>64,31%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>73,59%</t>
+          <t>74,25%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -10814,12 +10814,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>181372</t>
+          <t>180768</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>222399</t>
+          <t>219491</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -10829,12 +10829,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>48,01%</t>
+          <t>47,85%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>58,87%</t>
+          <t>58,1%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -10849,12 +10849,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>405466</t>
+          <t>405197</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>460298</t>
+          <t>459421</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -10864,12 +10864,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>56,94%</t>
+          <t>56,9%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>64,64%</t>
+          <t>64,52%</t>
         </is>
       </c>
     </row>
@@ -10892,12 +10892,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>56292</t>
+          <t>56583</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>86053</t>
+          <t>86354</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -10907,12 +10907,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>16,84%</t>
+          <t>16,92%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>25,74%</t>
+          <t>25,83%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -10927,12 +10927,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>102873</t>
+          <t>103580</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>141198</t>
+          <t>139964</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -10942,12 +10942,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>27,23%</t>
+          <t>27,42%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>37,38%</t>
+          <t>37,05%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -10962,12 +10962,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>168174</t>
+          <t>169160</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>220284</t>
+          <t>218129</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -10977,12 +10977,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>23,62%</t>
+          <t>23,76%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>30,93%</t>
+          <t>30,63%</t>
         </is>
       </c>
     </row>
@@ -11005,12 +11005,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>22942</t>
+          <t>22536</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>45080</t>
+          <t>42869</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -11020,12 +11020,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>6,86%</t>
+          <t>6,74%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>13,48%</t>
+          <t>12,82%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -11040,12 +11040,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>41823</t>
+          <t>41554</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>69459</t>
+          <t>68609</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -11055,12 +11055,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>11,07%</t>
+          <t>11,0%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>18,39%</t>
+          <t>18,16%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -11075,12 +11075,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>69928</t>
+          <t>70760</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>103467</t>
+          <t>104622</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -11090,12 +11090,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>9,82%</t>
+          <t>9,94%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>14,53%</t>
+          <t>14,69%</t>
         </is>
       </c>
     </row>
@@ -11235,12 +11235,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>99824</t>
+          <t>101263</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>128636</t>
+          <t>126987</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -11250,12 +11250,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>38,84%</t>
+          <t>39,4%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>50,05%</t>
+          <t>49,41%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -11270,12 +11270,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>100478</t>
+          <t>98322</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>141255</t>
+          <t>142371</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -11285,12 +11285,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>25,11%</t>
+          <t>24,57%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>35,3%</t>
+          <t>35,58%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -11305,12 +11305,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>206749</t>
+          <t>206992</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>260572</t>
+          <t>259318</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -11320,12 +11320,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>31,46%</t>
+          <t>31,5%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>39,65%</t>
+          <t>39,46%</t>
         </is>
       </c>
     </row>
@@ -11348,12 +11348,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>80747</t>
+          <t>80668</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>108325</t>
+          <t>107653</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -11363,12 +11363,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>31,42%</t>
+          <t>31,39%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>42,15%</t>
+          <t>41,89%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -11383,12 +11383,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>129218</t>
+          <t>128531</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>171950</t>
+          <t>170159</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -11398,12 +11398,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>32,29%</t>
+          <t>32,12%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>42,97%</t>
+          <t>42,52%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -11418,12 +11418,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>219367</t>
+          <t>221784</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>270685</t>
+          <t>272078</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -11433,12 +11433,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>33,38%</t>
+          <t>33,75%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>41,19%</t>
+          <t>41,4%</t>
         </is>
       </c>
     </row>
@@ -11461,12 +11461,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>39111</t>
+          <t>38577</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>61575</t>
+          <t>61772</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -11476,12 +11476,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>15,22%</t>
+          <t>15,01%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>23,96%</t>
+          <t>24,04%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -11496,12 +11496,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>110333</t>
+          <t>110914</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>155292</t>
+          <t>153707</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -11511,12 +11511,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>27,57%</t>
+          <t>27,72%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>38,81%</t>
+          <t>38,41%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -11531,12 +11531,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>155213</t>
+          <t>155200</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>204866</t>
+          <t>203538</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -11551,7 +11551,7 @@
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>31,17%</t>
+          <t>30,97%</t>
         </is>
       </c>
     </row>
@@ -11691,12 +11691,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>2881758</t>
+          <t>2877214</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>2960466</t>
+          <t>2961766</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -11706,12 +11706,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>84,9%</t>
+          <t>84,76%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>87,22%</t>
+          <t>87,26%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -11726,12 +11726,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>2689490</t>
+          <t>2690030</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>2795589</t>
+          <t>2792964</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -11741,12 +11741,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>75,88%</t>
+          <t>75,89%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>78,87%</t>
+          <t>78,8%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -11761,12 +11761,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>5595361</t>
+          <t>5599692</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>5727800</t>
+          <t>5733595</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -11776,12 +11776,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>80,64%</t>
+          <t>80,7%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>82,55%</t>
+          <t>82,63%</t>
         </is>
       </c>
     </row>
@@ -11804,12 +11804,12 @@
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>292558</t>
+          <t>289822</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>362239</t>
+          <t>361242</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
@@ -11819,12 +11819,12 @@
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>8,62%</t>
+          <t>8,54%</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>10,67%</t>
+          <t>10,64%</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
@@ -11839,12 +11839,12 @@
       </c>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>457093</t>
+          <t>458988</t>
         </is>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>543704</t>
+          <t>543207</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
@@ -11854,12 +11854,12 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>12,9%</t>
+          <t>12,95%</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
         <is>
-          <t>15,34%</t>
+          <t>15,33%</t>
         </is>
       </c>
       <c r="Q33" s="2" t="inlineStr">
@@ -11874,12 +11874,12 @@
       </c>
       <c r="S33" s="2" t="inlineStr">
         <is>
-          <t>772737</t>
+          <t>768341</t>
         </is>
       </c>
       <c r="T33" s="2" t="inlineStr">
         <is>
-          <t>876990</t>
+          <t>881772</t>
         </is>
       </c>
       <c r="U33" s="2" t="inlineStr">
@@ -11889,12 +11889,12 @@
       </c>
       <c r="V33" s="2" t="inlineStr">
         <is>
-          <t>11,14%</t>
+          <t>11,07%</t>
         </is>
       </c>
       <c r="W33" s="2" t="inlineStr">
         <is>
-          <t>12,64%</t>
+          <t>12,71%</t>
         </is>
       </c>
     </row>
@@ -11917,12 +11917,12 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>124595</t>
+          <t>123579</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>171432</t>
+          <t>171287</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -11932,7 +11932,7 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>3,67%</t>
+          <t>3,64%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
@@ -11952,12 +11952,12 @@
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>265319</t>
+          <t>266832</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>336190</t>
+          <t>336917</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -11967,12 +11967,12 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>7,49%</t>
+          <t>7,53%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>9,48%</t>
+          <t>9,51%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -11987,12 +11987,12 @@
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>404263</t>
+          <t>404517</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>493691</t>
+          <t>486863</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -12007,7 +12007,7 @@
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>7,11%</t>
+          <t>7,02%</t>
         </is>
       </c>
     </row>
@@ -12187,7 +12187,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según limitación a hacer esfuerzos moderados en 2023</t>
+          <t>Población según limitación a hacer esfuerzos moderados en 2023 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -12382,12 +12382,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>375391</t>
+          <t>376978</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>398313</t>
+          <t>398267</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -12397,12 +12397,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>93,85%</t>
+          <t>94,25%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>99,58%</t>
+          <t>99,57%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -12417,12 +12417,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>303380</t>
+          <t>303718</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>313034</t>
+          <t>313037</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -12432,7 +12432,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>96,86%</t>
+          <t>96,97%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -12452,12 +12452,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>686530</t>
+          <t>683573</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>709772</t>
+          <t>709231</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -12467,12 +12467,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>96,26%</t>
+          <t>95,85%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>99,52%</t>
+          <t>99,45%</t>
         </is>
       </c>
     </row>
@@ -12495,12 +12495,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>1674</t>
+          <t>1720</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>24596</t>
+          <t>23009</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -12510,12 +12510,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0,42%</t>
+          <t>0,43%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>6,15%</t>
+          <t>5,75%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -12535,7 +12535,7 @@
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>6011</t>
+          <t>6500</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -12550,7 +12550,7 @@
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>1,92%</t>
+          <t>2,08%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -12565,12 +12565,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1939</t>
+          <t>1933</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>25755</t>
+          <t>26884</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -12585,7 +12585,7 @@
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>3,61%</t>
+          <t>3,77%</t>
         </is>
       </c>
     </row>
@@ -12608,74 +12608,74 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K6" s="2" t="inlineStr">
+        <is>
+          <t>1784</t>
+        </is>
+      </c>
+      <c r="L6" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>4435</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
+      <c r="M6" s="2" t="inlineStr">
+        <is>
+          <t>9285</t>
+        </is>
+      </c>
+      <c r="N6" s="2" t="inlineStr">
+        <is>
+          <t>0,57%</t>
+        </is>
+      </c>
+      <c r="O6" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>1,11%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
+      <c r="P6" s="2" t="inlineStr">
+        <is>
+          <t>2,96%</t>
+        </is>
+      </c>
+      <c r="Q6" s="2" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="K6" s="2" t="inlineStr">
+      <c r="R6" s="2" t="inlineStr">
         <is>
           <t>1784</t>
         </is>
       </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>155</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>8459</t>
-        </is>
-      </c>
-      <c r="N6" s="2" t="inlineStr">
-        <is>
-          <t>0,57%</t>
-        </is>
-      </c>
-      <c r="O6" s="2" t="inlineStr">
-        <is>
-          <t>0,05%</t>
-        </is>
-      </c>
-      <c r="P6" s="2" t="inlineStr">
-        <is>
-          <t>2,7%</t>
-        </is>
-      </c>
-      <c r="Q6" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="R6" s="2" t="inlineStr">
-        <is>
-          <t>1784</t>
-        </is>
-      </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
           <t>0</t>
@@ -12683,7 +12683,7 @@
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>10211</t>
+          <t>9861</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -12698,7 +12698,7 @@
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>1,43%</t>
+          <t>1,38%</t>
         </is>
       </c>
     </row>
@@ -12838,12 +12838,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>386833</t>
+          <t>386083</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>410208</t>
+          <t>410311</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -12853,12 +12853,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>91,33%</t>
+          <t>91,15%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>96,85%</t>
+          <t>96,88%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -12873,12 +12873,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>500232</t>
+          <t>499534</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>509936</t>
+          <t>510216</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -12888,12 +12888,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>97,68%</t>
+          <t>97,55%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>99,58%</t>
+          <t>99,63%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -12908,12 +12908,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>890641</t>
+          <t>891223</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>919083</t>
+          <t>918988</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -12923,12 +12923,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>95,19%</t>
+          <t>95,25%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>98,23%</t>
+          <t>98,22%</t>
         </is>
       </c>
     </row>
@@ -12951,12 +12951,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>8797</t>
+          <t>8994</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>31595</t>
+          <t>31980</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -12966,12 +12966,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>2,08%</t>
+          <t>2,12%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>7,46%</t>
+          <t>7,55%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -12986,12 +12986,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>1417</t>
+          <t>1577</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>10958</t>
+          <t>11645</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -13001,12 +13001,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>0,28%</t>
+          <t>0,31%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>2,14%</t>
+          <t>2,27%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -13021,12 +13021,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>12352</t>
+          <t>12500</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>37787</t>
+          <t>38229</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -13036,12 +13036,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>1,32%</t>
+          <t>1,34%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>4,04%</t>
+          <t>4,09%</t>
         </is>
       </c>
     </row>
@@ -13064,12 +13064,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>1380</t>
+          <t>1449</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>11504</t>
+          <t>11998</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -13079,12 +13079,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>0,33%</t>
+          <t>0,34%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>2,72%</t>
+          <t>2,83%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -13104,7 +13104,7 @@
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>4552</t>
+          <t>5367</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -13119,7 +13119,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>0,89%</t>
+          <t>1,05%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -13134,12 +13134,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>2220</t>
+          <t>2111</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>12611</t>
+          <t>13039</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -13149,12 +13149,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>0,24%</t>
+          <t>0,23%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>1,35%</t>
+          <t>1,39%</t>
         </is>
       </c>
     </row>
@@ -13294,12 +13294,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>493691</t>
+          <t>492720</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>515716</t>
+          <t>515241</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -13309,12 +13309,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>92,05%</t>
+          <t>91,87%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>96,16%</t>
+          <t>96,07%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -13329,12 +13329,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>537521</t>
+          <t>537117</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>560149</t>
+          <t>561799</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -13344,12 +13344,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>90,88%</t>
+          <t>90,81%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>94,71%</t>
+          <t>94,99%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -13364,12 +13364,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>1038026</t>
+          <t>1038036</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>1070211</t>
+          <t>1069839</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -13384,7 +13384,7 @@
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>94,89%</t>
+          <t>94,86%</t>
         </is>
       </c>
     </row>
@@ -13407,12 +13407,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>17498</t>
+          <t>18100</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>38374</t>
+          <t>38987</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -13422,12 +13422,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>3,26%</t>
+          <t>3,37%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>7,15%</t>
+          <t>7,27%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -13442,12 +13442,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>22768</t>
+          <t>21472</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>41996</t>
+          <t>42687</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -13457,12 +13457,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>3,85%</t>
+          <t>3,63%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>7,1%</t>
+          <t>7,22%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -13477,12 +13477,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>45199</t>
+          <t>45617</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>74290</t>
+          <t>74425</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -13492,12 +13492,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>4,01%</t>
+          <t>4,04%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>6,59%</t>
+          <t>6,6%</t>
         </is>
       </c>
     </row>
@@ -13520,12 +13520,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>1041</t>
+          <t>1053</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>9643</t>
+          <t>10584</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -13535,12 +13535,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>0,19%</t>
+          <t>0,2%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>1,8%</t>
+          <t>1,97%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -13555,12 +13555,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>6063</t>
+          <t>5921</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>17754</t>
+          <t>17432</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -13570,12 +13570,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>1,03%</t>
+          <t>1,0%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>3,0%</t>
+          <t>2,95%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -13590,12 +13590,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>8949</t>
+          <t>8933</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>22971</t>
+          <t>22432</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -13610,7 +13610,7 @@
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>2,04%</t>
+          <t>1,99%</t>
         </is>
       </c>
     </row>
@@ -13750,12 +13750,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>253012</t>
+          <t>236738</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>794095</t>
+          <t>794662</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -13765,12 +13765,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>28,5%</t>
+          <t>26,67%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>89,45%</t>
+          <t>89,51%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -13785,12 +13785,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>594936</t>
+          <t>595539</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>633478</t>
+          <t>632476</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -13800,12 +13800,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>83,46%</t>
+          <t>83,54%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>88,86%</t>
+          <t>88,72%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -13820,12 +13820,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>701338</t>
+          <t>782729</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>1406659</t>
+          <t>1407067</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -13835,12 +13835,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>43,82%</t>
+          <t>48,9%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>87,88%</t>
+          <t>87,91%</t>
         </is>
       </c>
     </row>
@@ -13863,12 +13863,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>58209</t>
+          <t>59840</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>620508</t>
+          <t>639445</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -13878,12 +13878,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>6,56%</t>
+          <t>6,74%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>69,89%</t>
+          <t>72,03%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -13898,12 +13898,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>59098</t>
+          <t>61759</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>93772</t>
+          <t>95444</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -13913,12 +13913,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>8,29%</t>
+          <t>8,66%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>13,15%</t>
+          <t>13,39%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -13933,12 +13933,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>137856</t>
+          <t>137876</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>869839</t>
+          <t>779048</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -13953,7 +13953,7 @@
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>54,34%</t>
+          <t>48,67%</t>
         </is>
       </c>
     </row>
@@ -13976,12 +13976,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>9422</t>
+          <t>10386</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>42586</t>
+          <t>43002</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -13991,12 +13991,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>1,06%</t>
+          <t>1,17%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>4,8%</t>
+          <t>4,84%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -14011,12 +14011,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>15323</t>
+          <t>15219</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>31023</t>
+          <t>29699</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -14026,12 +14026,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>2,15%</t>
+          <t>2,13%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>4,35%</t>
+          <t>4,17%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -14046,12 +14046,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>28443</t>
+          <t>28946</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>64598</t>
+          <t>66022</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -14061,12 +14061,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>1,78%</t>
+          <t>1,81%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>4,04%</t>
+          <t>4,12%</t>
         </is>
       </c>
     </row>
@@ -14206,12 +14206,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>427287</t>
+          <t>429248</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>466219</t>
+          <t>465511</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -14221,12 +14221,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>76,13%</t>
+          <t>76,48%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>83,07%</t>
+          <t>82,94%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -14241,12 +14241,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>395358</t>
+          <t>396860</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>426198</t>
+          <t>427095</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -14256,12 +14256,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>72,16%</t>
+          <t>72,43%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>77,79%</t>
+          <t>77,95%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -14276,12 +14276,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>833399</t>
+          <t>833143</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>882130</t>
+          <t>881532</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -14291,12 +14291,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>75,14%</t>
+          <t>75,12%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>79,53%</t>
+          <t>79,48%</t>
         </is>
       </c>
     </row>
@@ -14319,12 +14319,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>67013</t>
+          <t>68705</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>100792</t>
+          <t>101358</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -14334,12 +14334,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>11,94%</t>
+          <t>12,24%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>17,96%</t>
+          <t>18,06%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -14354,12 +14354,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>87095</t>
+          <t>87177</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>113550</t>
+          <t>113509</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -14369,7 +14369,7 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>15,9%</t>
+          <t>15,91%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
@@ -14389,12 +14389,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>163284</t>
+          <t>161932</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>206070</t>
+          <t>206491</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -14404,12 +14404,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>14,72%</t>
+          <t>14,6%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>18,58%</t>
+          <t>18,62%</t>
         </is>
       </c>
     </row>
@@ -14432,12 +14432,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>21056</t>
+          <t>21120</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>41558</t>
+          <t>40231</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -14447,12 +14447,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>3,75%</t>
+          <t>3,76%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>7,4%</t>
+          <t>7,17%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -14467,12 +14467,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>28877</t>
+          <t>28927</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>46317</t>
+          <t>46595</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -14482,12 +14482,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>5,27%</t>
+          <t>5,28%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>8,45%</t>
+          <t>8,5%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -14502,12 +14502,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>53802</t>
+          <t>54763</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>80126</t>
+          <t>80695</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -14517,12 +14517,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>4,85%</t>
+          <t>4,94%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>7,22%</t>
+          <t>7,28%</t>
         </is>
       </c>
     </row>
@@ -14662,12 +14662,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>270307</t>
+          <t>270971</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>295837</t>
+          <t>295473</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -14677,12 +14677,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>73,42%</t>
+          <t>73,6%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>80,35%</t>
+          <t>80,26%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -14697,12 +14697,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>366411</t>
+          <t>368306</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>541740</t>
+          <t>540187</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -14712,12 +14712,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>60,23%</t>
+          <t>60,54%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>89,05%</t>
+          <t>88,79%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -14732,12 +14732,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>666930</t>
+          <t>664803</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>847418</t>
+          <t>848811</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -14747,12 +14747,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>68,3%</t>
+          <t>68,08%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>86,78%</t>
+          <t>86,92%</t>
         </is>
       </c>
     </row>
@@ -14775,12 +14775,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>47988</t>
+          <t>48534</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>70516</t>
+          <t>69950</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -14790,12 +14790,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>13,03%</t>
+          <t>13,18%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>19,15%</t>
+          <t>19,0%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -14810,12 +14810,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>49392</t>
+          <t>51989</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>184556</t>
+          <t>184114</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -14825,12 +14825,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>8,12%</t>
+          <t>8,55%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>30,34%</t>
+          <t>30,26%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -14845,12 +14845,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>96117</t>
+          <t>92266</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>231096</t>
+          <t>230930</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -14860,12 +14860,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>9,84%</t>
+          <t>9,45%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>23,66%</t>
+          <t>23,65%</t>
         </is>
       </c>
     </row>
@@ -14888,12 +14888,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>18295</t>
+          <t>18921</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>35611</t>
+          <t>35573</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -14903,12 +14903,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>4,97%</t>
+          <t>5,14%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>9,67%</t>
+          <t>9,66%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -14923,12 +14923,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>14102</t>
+          <t>16154</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>60324</t>
+          <t>60478</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -14938,12 +14938,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>2,32%</t>
+          <t>2,66%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>9,92%</t>
+          <t>9,94%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -14958,12 +14958,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>34422</t>
+          <t>32354</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>85203</t>
+          <t>86478</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -14973,12 +14973,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>3,52%</t>
+          <t>3,31%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>8,73%</t>
+          <t>8,86%</t>
         </is>
       </c>
     </row>
@@ -15118,12 +15118,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>128103</t>
+          <t>128419</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>153969</t>
+          <t>156058</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -15133,12 +15133,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>45,3%</t>
+          <t>45,42%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>54,45%</t>
+          <t>55,19%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -15153,12 +15153,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>99512</t>
+          <t>99255</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>124786</t>
+          <t>123997</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -15168,12 +15168,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>23,37%</t>
+          <t>23,31%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>29,3%</t>
+          <t>29,12%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -15188,12 +15188,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>233408</t>
+          <t>234670</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>270448</t>
+          <t>271568</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -15203,12 +15203,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>32,94%</t>
+          <t>33,12%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>38,17%</t>
+          <t>38,33%</t>
         </is>
       </c>
     </row>
@@ -15231,12 +15231,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>77499</t>
+          <t>76653</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>101068</t>
+          <t>102686</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -15246,12 +15246,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>27,41%</t>
+          <t>27,11%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>35,74%</t>
+          <t>36,32%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -15266,12 +15266,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>144031</t>
+          <t>142197</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>172246</t>
+          <t>170520</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -15281,12 +15281,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>33,82%</t>
+          <t>33,39%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>40,45%</t>
+          <t>40,04%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -15301,12 +15301,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>228215</t>
+          <t>228622</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>267253</t>
+          <t>265839</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -15316,12 +15316,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>32,21%</t>
+          <t>32,26%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>37,72%</t>
+          <t>37,52%</t>
         </is>
       </c>
     </row>
@@ -15344,12 +15344,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>41827</t>
+          <t>42140</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>62226</t>
+          <t>62195</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -15359,12 +15359,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>14,79%</t>
+          <t>14,9%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>22,01%</t>
+          <t>22,0%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -15379,12 +15379,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>142850</t>
+          <t>143568</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>171007</t>
+          <t>171465</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -15394,12 +15394,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>33,55%</t>
+          <t>33,71%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>40,16%</t>
+          <t>40,27%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -15414,12 +15414,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>190910</t>
+          <t>191131</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>226491</t>
+          <t>227631</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -15429,12 +15429,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>26,94%</t>
+          <t>26,97%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>31,96%</t>
+          <t>32,12%</t>
         </is>
       </c>
     </row>
@@ -15574,12 +15574,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>2137231</t>
+          <t>2152743</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>2964823</t>
+          <t>2967652</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -15589,12 +15589,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>61,77%</t>
+          <t>62,22%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>85,69%</t>
+          <t>85,77%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -15609,12 +15609,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>2887911</t>
+          <t>2883793</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>3092455</t>
+          <t>3098624</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -15624,12 +15624,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>77,8%</t>
+          <t>77,69%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>83,32%</t>
+          <t>83,48%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -15644,12 +15644,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>4965288</t>
+          <t>5036625</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>5942834</t>
+          <t>5942376</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -15659,12 +15659,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>69,24%</t>
+          <t>70,23%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>82,87%</t>
+          <t>82,86%</t>
         </is>
       </c>
     </row>
@@ -15687,12 +15687,12 @@
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>346655</t>
+          <t>342667</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>1223273</t>
+          <t>1199362</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
@@ -15702,12 +15702,12 @@
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>10,02%</t>
+          <t>9,9%</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>35,36%</t>
+          <t>34,67%</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
@@ -15722,12 +15722,12 @@
       </c>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>400445</t>
+          <t>392132</t>
         </is>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>535604</t>
+          <t>538496</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
@@ -15737,12 +15737,12 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>10,79%</t>
+          <t>10,56%</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
         <is>
-          <t>14,43%</t>
+          <t>14,51%</t>
         </is>
       </c>
       <c r="Q33" s="2" t="inlineStr">
@@ -15757,12 +15757,12 @@
       </c>
       <c r="S33" s="2" t="inlineStr">
         <is>
-          <t>816643</t>
+          <t>821386</t>
         </is>
       </c>
       <c r="T33" s="2" t="inlineStr">
         <is>
-          <t>1839966</t>
+          <t>1734167</t>
         </is>
       </c>
       <c r="U33" s="2" t="inlineStr">
@@ -15772,12 +15772,12 @@
       </c>
       <c r="V33" s="2" t="inlineStr">
         <is>
-          <t>11,39%</t>
+          <t>11,45%</t>
         </is>
       </c>
       <c r="W33" s="2" t="inlineStr">
         <is>
-          <t>25,66%</t>
+          <t>24,18%</t>
         </is>
       </c>
     </row>
@@ -15800,12 +15800,12 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>110518</t>
+          <t>107734</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>167483</t>
+          <t>165951</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -15815,12 +15815,12 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>3,19%</t>
+          <t>3,11%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>4,84%</t>
+          <t>4,8%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -15835,12 +15835,12 @@
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>216236</t>
+          <t>220567</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>295695</t>
+          <t>298997</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -15850,12 +15850,12 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>5,83%</t>
+          <t>5,94%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>7,97%</t>
+          <t>8,06%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -15870,12 +15870,12 @@
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>357799</t>
+          <t>353317</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>452106</t>
+          <t>451446</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -15885,12 +15885,12 @@
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>4,99%</t>
+          <t>4,93%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>6,3%</t>
+          <t>6,29%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/P0801-Edad-trans_orig.xlsx
+++ b/data/trans_orig/P0801-Edad-trans_orig.xlsx
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>478651</t>
+          <t>478378</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>490505</t>
+          <t>490243</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>96,88%</t>
+          <t>96,83%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>99,28%</t>
+          <t>99,23%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>447731</t>
+          <t>447983</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>461679</t>
+          <t>461787</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>95,77%</t>
+          <t>95,83%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>98,76%</t>
+          <t>98,78%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>929661</t>
+          <t>931457</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>949395</t>
+          <t>949215</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>96,68%</t>
+          <t>96,87%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>98,74%</t>
+          <t>98,72%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>2766</t>
+          <t>2794</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>14371</t>
+          <t>14180</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0,56%</t>
+          <t>0,57%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>2,91%</t>
+          <t>2,87%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>3124</t>
+          <t>3269</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>15313</t>
+          <t>15245</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>0,67%</t>
+          <t>0,7%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>3,28%</t>
+          <t>3,26%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>8624</t>
+          <t>8419</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>25620</t>
+          <t>25005</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>0,9%</t>
+          <t>0,88%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>2,66%</t>
+          <t>2,6%</t>
         </is>
       </c>
     </row>
@@ -964,7 +964,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>4803</t>
+          <t>4844</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -979,7 +979,7 @@
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>0,97%</t>
+          <t>0,98%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -994,12 +994,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>947</t>
+          <t>933</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>9393</t>
+          <t>9341</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1014,7 +1014,7 @@
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>2,01%</t>
+          <t>2,0%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1029,12 +1029,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>1816</t>
+          <t>1852</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>11212</t>
+          <t>10418</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1049,7 +1049,7 @@
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>1,17%</t>
+          <t>1,08%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>700501</t>
+          <t>700556</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>721787</t>
+          <t>721705</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>95,24%</t>
+          <t>95,25%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>98,14%</t>
+          <t>98,13%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>582049</t>
+          <t>581072</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>604582</t>
+          <t>603858</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>93,05%</t>
+          <t>92,9%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>96,66%</t>
+          <t>96,54%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1292369</t>
+          <t>1292107</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1321891</t>
+          <t>1321565</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>94,96%</t>
+          <t>94,94%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>97,13%</t>
+          <t>97,1%</t>
         </is>
       </c>
     </row>
@@ -1302,12 +1302,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>9074</t>
+          <t>9052</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>26036</t>
+          <t>27330</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1322,7 +1322,7 @@
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>3,54%</t>
+          <t>3,72%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1337,12 +1337,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>18121</t>
+          <t>19092</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>40478</t>
+          <t>40907</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1352,12 +1352,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>2,9%</t>
+          <t>3,05%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>6,47%</t>
+          <t>6,54%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1372,12 +1372,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>31262</t>
+          <t>31599</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>58946</t>
+          <t>58384</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1387,12 +1387,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>2,3%</t>
+          <t>2,32%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>4,33%</t>
+          <t>4,29%</t>
         </is>
       </c>
     </row>
@@ -1415,12 +1415,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>2406</t>
+          <t>2419</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>13790</t>
+          <t>13181</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1435,7 +1435,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>1,87%</t>
+          <t>1,79%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1450,12 +1450,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>931</t>
+          <t>934</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>8432</t>
+          <t>9512</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1470,42 +1470,42 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
+          <t>1,52%</t>
+        </is>
+      </c>
+      <c r="Q10" s="2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="R10" s="2" t="inlineStr">
+        <is>
+          <t>9491</t>
+        </is>
+      </c>
+      <c r="S10" s="2" t="inlineStr">
+        <is>
+          <t>4885</t>
+        </is>
+      </c>
+      <c r="T10" s="2" t="inlineStr">
+        <is>
+          <t>18376</t>
+        </is>
+      </c>
+      <c r="U10" s="2" t="inlineStr">
+        <is>
+          <t>0,7%</t>
+        </is>
+      </c>
+      <c r="V10" s="2" t="inlineStr">
+        <is>
+          <t>0,36%</t>
+        </is>
+      </c>
+      <c r="W10" s="2" t="inlineStr">
+        <is>
           <t>1,35%</t>
-        </is>
-      </c>
-      <c r="Q10" s="2" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="R10" s="2" t="inlineStr">
-        <is>
-          <t>9491</t>
-        </is>
-      </c>
-      <c r="S10" s="2" t="inlineStr">
-        <is>
-          <t>4890</t>
-        </is>
-      </c>
-      <c r="T10" s="2" t="inlineStr">
-        <is>
-          <t>18231</t>
-        </is>
-      </c>
-      <c r="U10" s="2" t="inlineStr">
-        <is>
-          <t>0,7%</t>
-        </is>
-      </c>
-      <c r="V10" s="2" t="inlineStr">
-        <is>
-          <t>0,36%</t>
-        </is>
-      </c>
-      <c r="W10" s="2" t="inlineStr">
-        <is>
-          <t>1,34%</t>
         </is>
       </c>
     </row>
@@ -1645,12 +1645,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>599936</t>
+          <t>600300</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>620579</t>
+          <t>620952</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1660,12 +1660,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>93,94%</t>
+          <t>93,99%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>97,17%</t>
+          <t>97,23%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1680,12 +1680,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>619001</t>
+          <t>619086</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>648653</t>
+          <t>647606</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1695,12 +1695,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>89,74%</t>
+          <t>89,76%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>94,04%</t>
+          <t>93,89%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1715,12 +1715,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>1228190</t>
+          <t>1227273</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>1262735</t>
+          <t>1264143</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1730,12 +1730,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>92,46%</t>
+          <t>92,39%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>95,06%</t>
+          <t>95,16%</t>
         </is>
       </c>
     </row>
@@ -1758,12 +1758,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>12312</t>
+          <t>12221</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>31073</t>
+          <t>31370</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1773,12 +1773,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>1,93%</t>
+          <t>1,91%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>4,87%</t>
+          <t>4,91%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1793,12 +1793,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>33687</t>
+          <t>34370</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>61994</t>
+          <t>61284</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1808,12 +1808,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>4,88%</t>
+          <t>4,98%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>8,99%</t>
+          <t>8,88%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1828,12 +1828,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>52769</t>
+          <t>50945</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>84457</t>
+          <t>83875</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1843,12 +1843,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>3,97%</t>
+          <t>3,84%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>6,36%</t>
+          <t>6,31%</t>
         </is>
       </c>
     </row>
@@ -1871,12 +1871,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>2670</t>
+          <t>2664</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>12022</t>
+          <t>12211</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1891,7 +1891,7 @@
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>1,88%</t>
+          <t>1,91%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1906,12 +1906,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>4234</t>
+          <t>3790</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>16121</t>
+          <t>16922</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1921,12 +1921,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>0,61%</t>
+          <t>0,55%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>2,34%</t>
+          <t>2,45%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1941,12 +1941,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>8538</t>
+          <t>8445</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>24795</t>
+          <t>23741</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1961,7 +1961,7 @@
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>1,87%</t>
+          <t>1,79%</t>
         </is>
       </c>
     </row>
@@ -2101,12 +2101,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>469830</t>
+          <t>467172</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>492031</t>
+          <t>492090</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2116,12 +2116,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>90,5%</t>
+          <t>89,99%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>94,78%</t>
+          <t>94,79%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2136,12 +2136,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>420361</t>
+          <t>419033</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>453210</t>
+          <t>451540</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2151,12 +2151,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>81,52%</t>
+          <t>81,26%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>87,89%</t>
+          <t>87,57%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2171,12 +2171,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>896713</t>
+          <t>897849</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>937759</t>
+          <t>938881</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2186,12 +2186,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>86,66%</t>
+          <t>86,77%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>90,62%</t>
+          <t>90,73%</t>
         </is>
       </c>
     </row>
@@ -2214,12 +2214,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>17559</t>
+          <t>16964</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>38323</t>
+          <t>37994</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2229,12 +2229,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>3,38%</t>
+          <t>3,27%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>7,38%</t>
+          <t>7,32%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2249,12 +2249,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>47274</t>
+          <t>46561</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>75853</t>
+          <t>77232</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2264,12 +2264,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>9,17%</t>
+          <t>9,03%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>14,71%</t>
+          <t>14,98%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2284,12 +2284,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>70470</t>
+          <t>70453</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>105646</t>
+          <t>106402</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2304,7 +2304,7 @@
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>10,21%</t>
+          <t>10,28%</t>
         </is>
       </c>
     </row>
@@ -2327,12 +2327,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>5803</t>
+          <t>5718</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>18704</t>
+          <t>18737</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2342,12 +2342,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>1,12%</t>
+          <t>1,1%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>3,6%</t>
+          <t>3,61%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2362,12 +2362,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>11704</t>
+          <t>11434</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>28668</t>
+          <t>28518</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2377,12 +2377,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>2,27%</t>
+          <t>2,22%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>5,56%</t>
+          <t>5,53%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2397,12 +2397,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>20820</t>
+          <t>20074</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>41518</t>
+          <t>42093</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2412,12 +2412,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>2,01%</t>
+          <t>1,94%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>4,01%</t>
+          <t>4,07%</t>
         </is>
       </c>
     </row>
@@ -2557,12 +2557,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>292004</t>
+          <t>291055</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>323567</t>
+          <t>321381</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2572,12 +2572,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>75,51%</t>
+          <t>75,26%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>83,67%</t>
+          <t>83,11%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2592,12 +2592,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>273160</t>
+          <t>273355</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>308316</t>
+          <t>309211</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2607,12 +2607,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>67,62%</t>
+          <t>67,66%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>76,32%</t>
+          <t>76,54%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2627,12 +2627,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>573222</t>
+          <t>571975</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>621351</t>
+          <t>619997</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2642,12 +2642,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>72,5%</t>
+          <t>72,34%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>78,58%</t>
+          <t>78,41%</t>
         </is>
       </c>
     </row>
@@ -2670,12 +2670,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>46337</t>
+          <t>47032</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>73339</t>
+          <t>74218</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2685,12 +2685,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>11,98%</t>
+          <t>12,16%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>18,96%</t>
+          <t>19,19%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -2705,12 +2705,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>74820</t>
+          <t>73697</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>108457</t>
+          <t>107881</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2720,12 +2720,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>18,52%</t>
+          <t>18,24%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>26,85%</t>
+          <t>26,7%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2740,12 +2740,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>127439</t>
+          <t>130122</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>170974</t>
+          <t>170945</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2755,7 +2755,7 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>16,12%</t>
+          <t>16,46%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
@@ -2783,12 +2783,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>13107</t>
+          <t>12106</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>31817</t>
+          <t>30032</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2798,12 +2798,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>3,39%</t>
+          <t>3,13%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>8,23%</t>
+          <t>7,77%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2818,12 +2818,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>13977</t>
+          <t>13851</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>31805</t>
+          <t>32399</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2833,12 +2833,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>3,46%</t>
+          <t>3,43%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>7,87%</t>
+          <t>8,02%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2853,12 +2853,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>30514</t>
+          <t>31130</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>58461</t>
+          <t>56785</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2868,12 +2868,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>3,86%</t>
+          <t>3,94%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>7,39%</t>
+          <t>7,18%</t>
         </is>
       </c>
     </row>
@@ -3013,12 +3013,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>196298</t>
+          <t>198766</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>226402</t>
+          <t>227126</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3028,12 +3028,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>67,09%</t>
+          <t>67,93%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>77,38%</t>
+          <t>77,63%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3048,12 +3048,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>144707</t>
+          <t>143241</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>178943</t>
+          <t>177470</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3063,12 +3063,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>42,2%</t>
+          <t>41,77%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>52,18%</t>
+          <t>51,75%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3083,12 +3083,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>346540</t>
+          <t>350219</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>395300</t>
+          <t>398322</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3098,12 +3098,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>54,53%</t>
+          <t>55,11%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>62,2%</t>
+          <t>62,68%</t>
         </is>
       </c>
     </row>
@@ -3126,12 +3126,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>46266</t>
+          <t>46341</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>74247</t>
+          <t>72619</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3141,12 +3141,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>15,81%</t>
+          <t>15,84%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>25,38%</t>
+          <t>24,82%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3161,12 +3161,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>122161</t>
+          <t>122087</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>156025</t>
+          <t>156379</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3176,12 +3176,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>35,62%</t>
+          <t>35,6%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>45,5%</t>
+          <t>45,6%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3196,12 +3196,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>176906</t>
+          <t>174873</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>222696</t>
+          <t>221624</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3211,12 +3211,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>27,84%</t>
+          <t>27,52%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>35,04%</t>
+          <t>34,87%</t>
         </is>
       </c>
     </row>
@@ -3239,12 +3239,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>13395</t>
+          <t>13857</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>30922</t>
+          <t>30319</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3254,12 +3254,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>4,58%</t>
+          <t>4,74%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>10,57%</t>
+          <t>10,36%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3274,12 +3274,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>31803</t>
+          <t>32858</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>55578</t>
+          <t>57207</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3289,12 +3289,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>9,27%</t>
+          <t>9,58%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>16,21%</t>
+          <t>16,68%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3309,12 +3309,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>49587</t>
+          <t>49634</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>79285</t>
+          <t>79083</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3324,12 +3324,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>7,8%</t>
+          <t>7,81%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>12,48%</t>
+          <t>12,44%</t>
         </is>
       </c>
     </row>
@@ -3469,12 +3469,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>84668</t>
+          <t>84106</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>112318</t>
+          <t>112244</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3484,12 +3484,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>40,34%</t>
+          <t>40,07%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>53,51%</t>
+          <t>53,48%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3504,12 +3504,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>65794</t>
+          <t>63908</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>98150</t>
+          <t>97911</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3519,12 +3519,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>19,7%</t>
+          <t>19,14%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>29,39%</t>
+          <t>29,32%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3539,12 +3539,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>158033</t>
+          <t>157363</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>203367</t>
+          <t>201754</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3554,12 +3554,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>29,06%</t>
+          <t>28,94%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>37,4%</t>
+          <t>37,1%</t>
         </is>
       </c>
     </row>
@@ -3582,12 +3582,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>62615</t>
+          <t>62640</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>90824</t>
+          <t>89682</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3597,12 +3597,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>29,83%</t>
+          <t>29,85%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>43,27%</t>
+          <t>42,73%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3617,12 +3617,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>149229</t>
+          <t>150024</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>187522</t>
+          <t>188045</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3632,12 +3632,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>44,69%</t>
+          <t>44,93%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>56,16%</t>
+          <t>56,32%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3652,12 +3652,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>221863</t>
+          <t>221939</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>268364</t>
+          <t>268231</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3667,12 +3667,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>40,8%</t>
+          <t>40,81%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>49,35%</t>
+          <t>49,33%</t>
         </is>
       </c>
     </row>
@@ -3695,12 +3695,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>26342</t>
+          <t>26978</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>47158</t>
+          <t>47391</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -3710,12 +3710,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>12,55%</t>
+          <t>12,85%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>22,47%</t>
+          <t>22,58%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -3730,12 +3730,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>68679</t>
+          <t>67915</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>102986</t>
+          <t>101358</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -3745,12 +3745,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>20,57%</t>
+          <t>20,34%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>30,84%</t>
+          <t>30,36%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3765,12 +3765,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>101276</t>
+          <t>100173</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>140063</t>
+          <t>139775</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -3780,12 +3780,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>18,62%</t>
+          <t>18,42%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>25,76%</t>
+          <t>25,7%</t>
         </is>
       </c>
     </row>
@@ -3925,12 +3925,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>2876209</t>
+          <t>2873378</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>2946110</t>
+          <t>2944631</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -3940,12 +3940,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>87,78%</t>
+          <t>87,7%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>89,92%</t>
+          <t>89,87%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -3960,12 +3960,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>2605295</t>
+          <t>2600192</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>2701280</t>
+          <t>2696356</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -3975,12 +3975,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>77,1%</t>
+          <t>76,95%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>79,94%</t>
+          <t>79,79%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -3995,12 +3995,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>5510525</t>
+          <t>5501381</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>5624915</t>
+          <t>5625201</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -4010,12 +4010,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>82,79%</t>
+          <t>82,66%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>84,51%</t>
+          <t>84,52%</t>
         </is>
       </c>
     </row>
@@ -4038,12 +4038,12 @@
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>233979</t>
+          <t>234104</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>294603</t>
+          <t>296807</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
@@ -4058,7 +4058,7 @@
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>8,99%</t>
+          <t>9,06%</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
@@ -4073,12 +4073,12 @@
       </c>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>501078</t>
+          <t>504133</t>
         </is>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>587800</t>
+          <t>590426</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
@@ -4088,12 +4088,12 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>14,83%</t>
+          <t>14,92%</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
         <is>
-          <t>17,39%</t>
+          <t>17,47%</t>
         </is>
       </c>
       <c r="Q33" s="2" t="inlineStr">
@@ -4108,12 +4108,12 @@
       </c>
       <c r="S33" s="2" t="inlineStr">
         <is>
-          <t>751730</t>
+          <t>754279</t>
         </is>
       </c>
       <c r="T33" s="2" t="inlineStr">
         <is>
-          <t>855295</t>
+          <t>859064</t>
         </is>
       </c>
       <c r="U33" s="2" t="inlineStr">
@@ -4123,12 +4123,12 @@
       </c>
       <c r="V33" s="2" t="inlineStr">
         <is>
-          <t>11,29%</t>
+          <t>11,33%</t>
         </is>
       </c>
       <c r="W33" s="2" t="inlineStr">
         <is>
-          <t>12,85%</t>
+          <t>12,91%</t>
         </is>
       </c>
     </row>
@@ -4151,12 +4151,12 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>84180</t>
+          <t>84760</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>124806</t>
+          <t>124309</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -4166,12 +4166,12 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>2,57%</t>
+          <t>2,59%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>3,81%</t>
+          <t>3,79%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -4186,12 +4186,12 @@
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>156249</t>
+          <t>157790</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>209051</t>
+          <t>210321</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -4201,12 +4201,12 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>4,62%</t>
+          <t>4,67%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>6,19%</t>
+          <t>6,22%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -4221,12 +4221,12 @@
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>252141</t>
+          <t>251566</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>317893</t>
+          <t>317654</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -4236,12 +4236,12 @@
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>3,79%</t>
+          <t>3,78%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>4,78%</t>
+          <t>4,77%</t>
         </is>
       </c>
     </row>
@@ -4616,12 +4616,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>439073</t>
+          <t>439584</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>450478</t>
+          <t>450780</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -4631,12 +4631,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>96,68%</t>
+          <t>96,79%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>99,19%</t>
+          <t>99,26%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -4651,12 +4651,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>405597</t>
+          <t>405521</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>421670</t>
+          <t>422237</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -4666,12 +4666,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>94,27%</t>
+          <t>94,26%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>98,01%</t>
+          <t>98,14%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4686,12 +4686,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>849679</t>
+          <t>851644</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>869829</t>
+          <t>870644</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4701,12 +4701,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>96,08%</t>
+          <t>96,3%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>98,36%</t>
+          <t>98,45%</t>
         </is>
       </c>
     </row>
@@ -4729,12 +4729,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>2973</t>
+          <t>2822</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>14082</t>
+          <t>13795</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4744,12 +4744,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0,65%</t>
+          <t>0,62%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>3,1%</t>
+          <t>3,04%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4764,12 +4764,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>4899</t>
+          <t>4858</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>18447</t>
+          <t>19084</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4779,12 +4779,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>1,14%</t>
+          <t>1,13%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>4,29%</t>
+          <t>4,44%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4799,12 +4799,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>10121</t>
+          <t>9555</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>28152</t>
+          <t>25597</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4814,12 +4814,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>1,14%</t>
+          <t>1,08%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>3,18%</t>
+          <t>2,89%</t>
         </is>
       </c>
     </row>
@@ -4847,7 +4847,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>4345</t>
+          <t>6305</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -4862,7 +4862,7 @@
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>0,96%</t>
+          <t>1,39%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -4877,12 +4877,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>1907</t>
+          <t>1888</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>11042</t>
+          <t>10873</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -4897,7 +4897,7 @@
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>2,57%</t>
+          <t>2,53%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -4912,12 +4912,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>2007</t>
+          <t>2028</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>11781</t>
+          <t>12238</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -4932,7 +4932,7 @@
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>1,33%</t>
+          <t>1,38%</t>
         </is>
       </c>
     </row>
@@ -5072,12 +5072,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>651446</t>
+          <t>650318</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>671286</t>
+          <t>671494</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -5087,12 +5087,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>94,81%</t>
+          <t>94,65%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>97,7%</t>
+          <t>97,73%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -5107,12 +5107,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>569311</t>
+          <t>569010</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>591462</t>
+          <t>590810</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -5122,12 +5122,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>93,29%</t>
+          <t>93,24%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>96,92%</t>
+          <t>96,81%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -5142,12 +5142,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1229302</t>
+          <t>1227725</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1257980</t>
+          <t>1257563</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -5157,12 +5157,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>94,76%</t>
+          <t>94,63%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>96,97%</t>
+          <t>96,93%</t>
         </is>
       </c>
     </row>
@@ -5185,12 +5185,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>11358</t>
+          <t>11490</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>28651</t>
+          <t>29170</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -5200,12 +5200,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>1,65%</t>
+          <t>1,67%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>4,17%</t>
+          <t>4,25%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -5220,12 +5220,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>17860</t>
+          <t>18818</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>39951</t>
+          <t>40793</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -5235,12 +5235,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>2,93%</t>
+          <t>3,08%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>6,55%</t>
+          <t>6,68%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -5255,12 +5255,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>34475</t>
+          <t>33823</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>60230</t>
+          <t>62162</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -5270,12 +5270,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>2,66%</t>
+          <t>2,61%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>4,64%</t>
+          <t>4,79%</t>
         </is>
       </c>
     </row>
@@ -5298,12 +5298,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>1894</t>
+          <t>1873</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>14197</t>
+          <t>14126</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -5313,12 +5313,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>0,28%</t>
+          <t>0,27%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>2,07%</t>
+          <t>2,06%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -5338,7 +5338,7 @@
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>5229</t>
+          <t>6257</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -5353,7 +5353,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>0,86%</t>
+          <t>1,03%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -5368,12 +5368,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>2817</t>
+          <t>2715</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>14911</t>
+          <t>14449</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -5383,12 +5383,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>0,22%</t>
+          <t>0,21%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>1,15%</t>
+          <t>1,11%</t>
         </is>
       </c>
     </row>
@@ -5528,12 +5528,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>627063</t>
+          <t>624789</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>651996</t>
+          <t>651442</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -5543,12 +5543,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>91,96%</t>
+          <t>91,63%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>95,62%</t>
+          <t>95,54%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -5563,12 +5563,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>612381</t>
+          <t>612543</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>646783</t>
+          <t>648784</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -5578,12 +5578,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>86,15%</t>
+          <t>86,17%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>90,99%</t>
+          <t>91,27%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -5598,12 +5598,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>1247974</t>
+          <t>1248642</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>1291511</t>
+          <t>1290897</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -5613,12 +5613,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>89,61%</t>
+          <t>89,66%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>92,73%</t>
+          <t>92,69%</t>
         </is>
       </c>
     </row>
@@ -5641,12 +5641,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>20093</t>
+          <t>20811</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>40978</t>
+          <t>42478</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -5656,12 +5656,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>2,95%</t>
+          <t>3,05%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>6,01%</t>
+          <t>6,23%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5676,12 +5676,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>48308</t>
+          <t>48054</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>79430</t>
+          <t>79090</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5691,12 +5691,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>6,8%</t>
+          <t>6,76%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>11,17%</t>
+          <t>11,13%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5711,12 +5711,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>74383</t>
+          <t>72647</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>115979</t>
+          <t>111887</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5726,12 +5726,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>5,34%</t>
+          <t>5,22%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>8,33%</t>
+          <t>8,03%</t>
         </is>
       </c>
     </row>
@@ -5754,12 +5754,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>6654</t>
+          <t>5963</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>21290</t>
+          <t>21746</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5769,12 +5769,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>0,98%</t>
+          <t>0,87%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>3,12%</t>
+          <t>3,19%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5789,12 +5789,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>10501</t>
+          <t>9699</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>28578</t>
+          <t>27430</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5804,12 +5804,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>1,48%</t>
+          <t>1,36%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>4,02%</t>
+          <t>3,86%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5824,12 +5824,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>20127</t>
+          <t>19447</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>43332</t>
+          <t>43199</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5839,12 +5839,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>1,45%</t>
+          <t>1,4%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>3,11%</t>
+          <t>3,1%</t>
         </is>
       </c>
     </row>
@@ -5984,12 +5984,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>530630</t>
+          <t>532301</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>562205</t>
+          <t>564701</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -5999,12 +5999,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>86,33%</t>
+          <t>86,61%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>91,47%</t>
+          <t>91,88%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -6019,12 +6019,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>493955</t>
+          <t>491754</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>530846</t>
+          <t>530742</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -6034,12 +6034,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>80,16%</t>
+          <t>79,8%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>86,15%</t>
+          <t>86,13%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -6054,12 +6054,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>1035686</t>
+          <t>1037060</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>1084715</t>
+          <t>1083478</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -6069,12 +6069,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>84,15%</t>
+          <t>84,26%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>88,13%</t>
+          <t>88,03%</t>
         </is>
       </c>
     </row>
@@ -6097,12 +6097,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>40175</t>
+          <t>39218</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>68088</t>
+          <t>69239</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -6112,12 +6112,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>6,54%</t>
+          <t>6,38%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>11,08%</t>
+          <t>11,27%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -6132,12 +6132,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>64179</t>
+          <t>64022</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>97330</t>
+          <t>99572</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -6147,12 +6147,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>10,42%</t>
+          <t>10,39%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>15,8%</t>
+          <t>16,16%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -6167,12 +6167,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>110569</t>
+          <t>113044</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>155693</t>
+          <t>156372</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -6182,12 +6182,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>8,98%</t>
+          <t>9,18%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>12,65%</t>
+          <t>12,7%</t>
         </is>
       </c>
     </row>
@@ -6210,12 +6210,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>8214</t>
+          <t>7199</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>23475</t>
+          <t>22561</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -6225,12 +6225,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>1,34%</t>
+          <t>1,17%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>3,82%</t>
+          <t>3,67%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -6245,12 +6245,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>14745</t>
+          <t>14839</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>34960</t>
+          <t>35587</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -6260,12 +6260,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>2,39%</t>
+          <t>2,41%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>5,67%</t>
+          <t>5,78%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -6280,12 +6280,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>26506</t>
+          <t>27386</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>50311</t>
+          <t>52388</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -6295,12 +6295,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>2,15%</t>
+          <t>2,23%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>4,09%</t>
+          <t>4,26%</t>
         </is>
       </c>
     </row>
@@ -6440,12 +6440,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>327339</t>
+          <t>328055</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>361152</t>
+          <t>360970</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -6455,12 +6455,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>76,23%</t>
+          <t>76,39%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>84,1%</t>
+          <t>84,06%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -6475,12 +6475,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>258459</t>
+          <t>258990</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>300537</t>
+          <t>301736</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -6490,12 +6490,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>57,72%</t>
+          <t>57,84%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>67,11%</t>
+          <t>67,38%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -6510,12 +6510,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>598987</t>
+          <t>597688</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>656093</t>
+          <t>651515</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -6525,12 +6525,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>68,28%</t>
+          <t>68,13%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>74,79%</t>
+          <t>74,27%</t>
         </is>
       </c>
     </row>
@@ -6553,12 +6553,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>44294</t>
+          <t>44183</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>75785</t>
+          <t>72946</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -6568,12 +6568,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>10,31%</t>
+          <t>10,29%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>17,65%</t>
+          <t>16,99%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -6588,12 +6588,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>103442</t>
+          <t>102385</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>140025</t>
+          <t>142369</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -6603,12 +6603,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>23,1%</t>
+          <t>22,86%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>31,27%</t>
+          <t>31,79%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -6623,12 +6623,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>153391</t>
+          <t>153530</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>201506</t>
+          <t>202880</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -6638,12 +6638,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>17,49%</t>
+          <t>17,5%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>22,97%</t>
+          <t>23,13%</t>
         </is>
       </c>
     </row>
@@ -6666,12 +6666,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>18139</t>
+          <t>18522</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>39422</t>
+          <t>40058</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -6681,12 +6681,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>4,22%</t>
+          <t>4,31%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>9,18%</t>
+          <t>9,33%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -6701,12 +6701,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>35842</t>
+          <t>34810</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>62714</t>
+          <t>62104</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -6716,12 +6716,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>8,0%</t>
+          <t>7,77%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>14,0%</t>
+          <t>13,87%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -6736,12 +6736,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>58369</t>
+          <t>59253</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>92418</t>
+          <t>94417</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -6751,12 +6751,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>6,65%</t>
+          <t>6,75%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>10,54%</t>
+          <t>10,76%</t>
         </is>
       </c>
     </row>
@@ -6896,12 +6896,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>182899</t>
+          <t>184310</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>219882</t>
+          <t>219554</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -6911,12 +6911,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>59,04%</t>
+          <t>59,5%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>70,98%</t>
+          <t>70,87%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -6931,12 +6931,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>140735</t>
+          <t>141805</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>179216</t>
+          <t>181207</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -6946,12 +6946,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>39,76%</t>
+          <t>40,06%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>50,63%</t>
+          <t>51,19%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -6966,12 +6966,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>338205</t>
+          <t>334923</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>390553</t>
+          <t>389653</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -6981,12 +6981,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>50,95%</t>
+          <t>50,46%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>58,84%</t>
+          <t>58,7%</t>
         </is>
       </c>
     </row>
@@ -7009,12 +7009,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>56458</t>
+          <t>57322</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>88695</t>
+          <t>89228</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -7024,12 +7024,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>18,22%</t>
+          <t>18,5%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>28,63%</t>
+          <t>28,8%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -7044,12 +7044,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>107779</t>
+          <t>108587</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>143142</t>
+          <t>146734</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -7059,12 +7059,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>30,45%</t>
+          <t>30,67%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>40,44%</t>
+          <t>41,45%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -7079,12 +7079,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>174826</t>
+          <t>172510</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>220602</t>
+          <t>221946</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -7094,12 +7094,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>26,34%</t>
+          <t>25,99%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>33,23%</t>
+          <t>33,44%</t>
         </is>
       </c>
     </row>
@@ -7122,12 +7122,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>25439</t>
+          <t>24420</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>50352</t>
+          <t>48470</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -7137,12 +7137,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>8,21%</t>
+          <t>7,88%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>16,25%</t>
+          <t>15,65%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -7157,12 +7157,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>55473</t>
+          <t>53000</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>84079</t>
+          <t>83587</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -7172,12 +7172,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>15,67%</t>
+          <t>14,97%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>23,75%</t>
+          <t>23,61%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -7192,12 +7192,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>86726</t>
+          <t>85226</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>122059</t>
+          <t>124711</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -7207,12 +7207,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>13,07%</t>
+          <t>12,84%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>18,39%</t>
+          <t>18,79%</t>
         </is>
       </c>
     </row>
@@ -7352,12 +7352,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>66048</t>
+          <t>66019</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>97722</t>
+          <t>98341</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -7367,12 +7367,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>26,44%</t>
+          <t>26,42%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>39,11%</t>
+          <t>39,36%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -7387,12 +7387,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>58749</t>
+          <t>58836</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>90356</t>
+          <t>91287</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -7402,12 +7402,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>15,1%</t>
+          <t>15,13%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>23,23%</t>
+          <t>23,47%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -7422,12 +7422,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>133830</t>
+          <t>133971</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>180157</t>
+          <t>178973</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -7437,12 +7437,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>20,95%</t>
+          <t>20,97%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>28,2%</t>
+          <t>28,02%</t>
         </is>
       </c>
     </row>
@@ -7465,12 +7465,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>80142</t>
+          <t>81494</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>113713</t>
+          <t>113345</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -7480,12 +7480,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>32,08%</t>
+          <t>32,62%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>45,51%</t>
+          <t>45,36%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -7500,12 +7500,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>136663</t>
+          <t>133787</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>176992</t>
+          <t>175160</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -7515,12 +7515,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>35,13%</t>
+          <t>34,39%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>45,5%</t>
+          <t>45,03%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -7535,12 +7535,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>225791</t>
+          <t>227871</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>280723</t>
+          <t>279163</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -7550,12 +7550,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>35,34%</t>
+          <t>35,67%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>43,94%</t>
+          <t>43,7%</t>
         </is>
       </c>
     </row>
@@ -7578,12 +7578,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>56302</t>
+          <t>57170</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>89066</t>
+          <t>88822</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -7593,12 +7593,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>22,53%</t>
+          <t>22,88%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>35,65%</t>
+          <t>35,55%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -7613,12 +7613,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>140562</t>
+          <t>140356</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>181201</t>
+          <t>181038</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -7628,12 +7628,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>36,14%</t>
+          <t>36,08%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>46,58%</t>
+          <t>46,54%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -7648,12 +7648,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>205843</t>
+          <t>204804</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>259968</t>
+          <t>257227</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -7663,12 +7663,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>32,22%</t>
+          <t>32,06%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>40,69%</t>
+          <t>40,27%</t>
         </is>
       </c>
     </row>
@@ -7808,12 +7808,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>2881731</t>
+          <t>2882611</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>2967405</t>
+          <t>2970587</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -7823,12 +7823,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>84,09%</t>
+          <t>84,12%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>86,59%</t>
+          <t>86,69%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -7843,12 +7843,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>2608515</t>
+          <t>2601302</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>2712998</t>
+          <t>2706798</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -7858,12 +7858,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>73,31%</t>
+          <t>73,11%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>76,24%</t>
+          <t>76,07%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -7878,12 +7878,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>5513816</t>
+          <t>5505234</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>5647275</t>
+          <t>5641435</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -7893,12 +7893,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>78,94%</t>
+          <t>78,81%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>80,85%</t>
+          <t>80,76%</t>
         </is>
       </c>
     </row>
@@ -7921,12 +7921,12 @@
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>299585</t>
+          <t>297225</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>371052</t>
+          <t>370202</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
@@ -7936,12 +7936,12 @@
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>8,74%</t>
+          <t>8,67%</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>10,83%</t>
+          <t>10,8%</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
@@ -7956,12 +7956,12 @@
       </c>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>534866</t>
+          <t>536321</t>
         </is>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>625028</t>
+          <t>623519</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
@@ -7971,12 +7971,12 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>15,03%</t>
+          <t>15,07%</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
         <is>
-          <t>17,57%</t>
+          <t>17,52%</t>
         </is>
       </c>
       <c r="Q33" s="2" t="inlineStr">
@@ -7991,12 +7991,12 @@
       </c>
       <c r="S33" s="2" t="inlineStr">
         <is>
-          <t>855193</t>
+          <t>859213</t>
         </is>
       </c>
       <c r="T33" s="2" t="inlineStr">
         <is>
-          <t>975111</t>
+          <t>969028</t>
         </is>
       </c>
       <c r="U33" s="2" t="inlineStr">
@@ -8006,12 +8006,12 @@
       </c>
       <c r="V33" s="2" t="inlineStr">
         <is>
-          <t>12,24%</t>
+          <t>12,3%</t>
         </is>
       </c>
       <c r="W33" s="2" t="inlineStr">
         <is>
-          <t>13,96%</t>
+          <t>13,87%</t>
         </is>
       </c>
     </row>
@@ -8034,12 +8034,12 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>141356</t>
+          <t>141259</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>194331</t>
+          <t>196134</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -8049,12 +8049,12 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>4,13%</t>
+          <t>4,12%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>5,67%</t>
+          <t>5,72%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -8069,12 +8069,12 @@
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>286207</t>
+          <t>286307</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>356685</t>
+          <t>359176</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -8084,12 +8084,12 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>8,04%</t>
+          <t>8,05%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>10,02%</t>
+          <t>10,09%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -8104,12 +8104,12 @@
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>443843</t>
+          <t>443201</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>531141</t>
+          <t>538790</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -8119,12 +8119,12 @@
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>6,35%</t>
+          <t>6,34%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>7,6%</t>
+          <t>7,71%</t>
         </is>
       </c>
     </row>
@@ -8499,7 +8499,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>411450</t>
+          <t>411608</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -8514,7 +8514,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>98,09%</t>
+          <t>98,13%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -8534,12 +8534,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>375791</t>
+          <t>375987</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>389213</t>
+          <t>389284</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -8549,12 +8549,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>94,96%</t>
+          <t>95,0%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>98,35%</t>
+          <t>98,36%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -8569,12 +8569,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>792426</t>
+          <t>791830</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>806848</t>
+          <t>807208</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -8584,12 +8584,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>97,2%</t>
+          <t>97,13%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>98,97%</t>
+          <t>99,02%</t>
         </is>
       </c>
     </row>
@@ -8617,7 +8617,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>8013</t>
+          <t>7855</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -8632,7 +8632,7 @@
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>1,91%</t>
+          <t>1,87%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -8647,12 +8647,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>5645</t>
+          <t>5626</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>18673</t>
+          <t>19224</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -8662,12 +8662,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>1,43%</t>
+          <t>1,42%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>4,72%</t>
+          <t>4,86%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -8682,12 +8682,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>7448</t>
+          <t>7438</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>21271</t>
+          <t>22784</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -8702,7 +8702,7 @@
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>2,61%</t>
+          <t>2,79%</t>
         </is>
       </c>
     </row>
@@ -8765,7 +8765,7 @@
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>5788</t>
+          <t>5296</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -8780,7 +8780,7 @@
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>1,46%</t>
+          <t>1,34%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -8800,7 +8800,7 @@
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>5802</t>
+          <t>4129</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -8815,7 +8815,7 @@
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>0,71%</t>
+          <t>0,51%</t>
         </is>
       </c>
     </row>
@@ -8955,12 +8955,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>559479</t>
+          <t>559123</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>578337</t>
+          <t>578528</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -8970,12 +8970,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>94,75%</t>
+          <t>94,69%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>97,94%</t>
+          <t>97,97%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -8990,12 +8990,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>525382</t>
+          <t>526883</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>546340</t>
+          <t>547336</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -9005,12 +9005,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>93,23%</t>
+          <t>93,49%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>96,95%</t>
+          <t>97,12%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -9025,12 +9025,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1093209</t>
+          <t>1093866</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1120870</t>
+          <t>1121454</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -9040,12 +9040,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>94,73%</t>
+          <t>94,79%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>97,13%</t>
+          <t>97,18%</t>
         </is>
       </c>
     </row>
@@ -9068,12 +9068,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>7585</t>
+          <t>7717</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>23685</t>
+          <t>24194</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -9083,12 +9083,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>1,28%</t>
+          <t>1,31%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>4,01%</t>
+          <t>4,1%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -9103,12 +9103,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>9524</t>
+          <t>9302</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>25460</t>
+          <t>24493</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -9118,12 +9118,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>1,69%</t>
+          <t>1,65%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>4,52%</t>
+          <t>4,35%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -9138,12 +9138,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>20686</t>
+          <t>20190</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>43597</t>
+          <t>42387</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -9153,12 +9153,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>1,79%</t>
+          <t>1,75%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>3,78%</t>
+          <t>3,67%</t>
         </is>
       </c>
     </row>
@@ -9181,12 +9181,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>1992</t>
+          <t>2022</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>12780</t>
+          <t>11874</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -9201,7 +9201,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>2,16%</t>
+          <t>2,01%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -9216,12 +9216,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>4675</t>
+          <t>4601</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>17448</t>
+          <t>17414</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -9231,12 +9231,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>0,83%</t>
+          <t>0,82%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>3,1%</t>
+          <t>3,09%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -9251,12 +9251,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>8867</t>
+          <t>8652</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>25384</t>
+          <t>24819</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -9266,12 +9266,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>0,77%</t>
+          <t>0,75%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>2,2%</t>
+          <t>2,15%</t>
         </is>
       </c>
     </row>
@@ -9411,12 +9411,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>620209</t>
+          <t>618715</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>644244</t>
+          <t>644107</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -9426,12 +9426,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>92,69%</t>
+          <t>92,47%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>96,29%</t>
+          <t>96,27%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -9446,12 +9446,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>597038</t>
+          <t>597161</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>624715</t>
+          <t>624123</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -9461,12 +9461,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>90,27%</t>
+          <t>90,29%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>94,46%</t>
+          <t>94,37%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -9481,12 +9481,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>1227117</t>
+          <t>1227040</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>1263112</t>
+          <t>1262035</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -9501,7 +9501,7 @@
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>94,94%</t>
+          <t>94,86%</t>
         </is>
       </c>
     </row>
@@ -9524,12 +9524,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>18364</t>
+          <t>19124</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>39699</t>
+          <t>41154</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -9539,12 +9539,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>2,74%</t>
+          <t>2,86%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>5,93%</t>
+          <t>6,15%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -9559,12 +9559,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>28986</t>
+          <t>29300</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>55222</t>
+          <t>54549</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -9574,12 +9574,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>4,38%</t>
+          <t>4,43%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>8,35%</t>
+          <t>8,25%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -9594,12 +9594,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>53290</t>
+          <t>54690</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>86166</t>
+          <t>87368</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -9609,12 +9609,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>4,01%</t>
+          <t>4,11%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>6,48%</t>
+          <t>6,57%</t>
         </is>
       </c>
     </row>
@@ -9637,12 +9637,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>3030</t>
+          <t>2868</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>14615</t>
+          <t>13393</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -9652,12 +9652,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>0,45%</t>
+          <t>0,43%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>2,18%</t>
+          <t>2,0%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -9672,12 +9672,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>3804</t>
+          <t>4071</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>15709</t>
+          <t>16005</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -9687,12 +9687,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>0,58%</t>
+          <t>0,62%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>2,38%</t>
+          <t>2,42%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -9707,12 +9707,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>9391</t>
+          <t>9340</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>24563</t>
+          <t>25918</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -9722,12 +9722,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>0,71%</t>
+          <t>0,7%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>1,85%</t>
+          <t>1,95%</t>
         </is>
       </c>
     </row>
@@ -9867,12 +9867,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>552140</t>
+          <t>552042</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>585430</t>
+          <t>586169</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -9882,12 +9882,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>85,46%</t>
+          <t>85,45%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>90,62%</t>
+          <t>90,73%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -9902,12 +9902,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>528984</t>
+          <t>529866</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>565849</t>
+          <t>564857</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -9917,12 +9917,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>81,5%</t>
+          <t>81,63%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>87,18%</t>
+          <t>87,02%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -9937,12 +9937,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>1092113</t>
+          <t>1090049</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>1142919</t>
+          <t>1142610</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -9952,12 +9952,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>84,32%</t>
+          <t>84,17%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>88,25%</t>
+          <t>88,22%</t>
         </is>
       </c>
     </row>
@@ -9980,12 +9980,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>35567</t>
+          <t>36381</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>64028</t>
+          <t>62710</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -9995,12 +9995,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>5,51%</t>
+          <t>5,63%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>9,91%</t>
+          <t>9,71%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -10015,12 +10015,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>48481</t>
+          <t>47859</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>78929</t>
+          <t>78138</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -10030,12 +10030,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>7,47%</t>
+          <t>7,37%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>12,16%</t>
+          <t>12,04%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -10050,12 +10050,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>91557</t>
+          <t>89906</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>132440</t>
+          <t>131382</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -10065,12 +10065,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>7,07%</t>
+          <t>6,94%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>10,23%</t>
+          <t>10,14%</t>
         </is>
       </c>
     </row>
@@ -10093,12 +10093,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>17934</t>
+          <t>18079</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>38931</t>
+          <t>39572</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -10108,12 +10108,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>2,78%</t>
+          <t>2,8%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>6,03%</t>
+          <t>6,13%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -10128,12 +10128,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>28765</t>
+          <t>27255</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>54036</t>
+          <t>53786</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -10143,12 +10143,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>4,43%</t>
+          <t>4,2%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>8,32%</t>
+          <t>8,29%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -10163,12 +10163,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>51032</t>
+          <t>51713</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>83902</t>
+          <t>86220</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -10178,12 +10178,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>3,94%</t>
+          <t>3,99%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>6,48%</t>
+          <t>6,66%</t>
         </is>
       </c>
     </row>
@@ -10323,12 +10323,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>365871</t>
+          <t>367148</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>403579</t>
+          <t>404659</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -10338,12 +10338,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>76,56%</t>
+          <t>76,82%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>84,45%</t>
+          <t>84,67%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -10358,12 +10358,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>315966</t>
+          <t>317575</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>359902</t>
+          <t>360531</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -10373,12 +10373,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>63,59%</t>
+          <t>63,92%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>72,44%</t>
+          <t>72,56%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -10393,12 +10393,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>698452</t>
+          <t>698608</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>755955</t>
+          <t>757076</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -10408,12 +10408,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>71,65%</t>
+          <t>71,67%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>77,55%</t>
+          <t>77,67%</t>
         </is>
       </c>
     </row>
@@ -10436,12 +10436,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>52282</t>
+          <t>51685</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>84648</t>
+          <t>83197</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -10451,12 +10451,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>10,94%</t>
+          <t>10,81%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>17,71%</t>
+          <t>17,41%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -10471,12 +10471,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>83448</t>
+          <t>83181</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>119315</t>
+          <t>121289</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -10486,12 +10486,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>16,8%</t>
+          <t>16,74%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>24,01%</t>
+          <t>24,41%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -10506,12 +10506,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>145841</t>
+          <t>141339</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>195360</t>
+          <t>192865</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -10521,12 +10521,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>14,96%</t>
+          <t>14,5%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>20,04%</t>
+          <t>19,79%</t>
         </is>
       </c>
     </row>
@@ -10549,12 +10549,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>14418</t>
+          <t>15536</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>37400</t>
+          <t>36415</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -10564,12 +10564,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>3,02%</t>
+          <t>3,25%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>7,83%</t>
+          <t>7,62%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -10584,12 +10584,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>42954</t>
+          <t>42664</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>72813</t>
+          <t>71800</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -10599,12 +10599,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>8,65%</t>
+          <t>8,59%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>14,65%</t>
+          <t>14,45%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -10619,12 +10619,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>63486</t>
+          <t>62990</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>103127</t>
+          <t>99353</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -10634,12 +10634,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>6,51%</t>
+          <t>6,46%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>10,58%</t>
+          <t>10,19%</t>
         </is>
       </c>
     </row>
@@ -10779,12 +10779,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>215014</t>
+          <t>212872</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>248229</t>
+          <t>246868</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -10794,12 +10794,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>64,31%</t>
+          <t>63,67%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>74,25%</t>
+          <t>73,84%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -10814,12 +10814,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>180768</t>
+          <t>180973</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>219491</t>
+          <t>220676</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -10829,12 +10829,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>47,85%</t>
+          <t>47,91%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>58,1%</t>
+          <t>58,42%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -10849,12 +10849,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>405197</t>
+          <t>406792</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>459421</t>
+          <t>456594</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -10864,12 +10864,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>56,9%</t>
+          <t>57,13%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>64,52%</t>
+          <t>64,12%</t>
         </is>
       </c>
     </row>
@@ -10892,12 +10892,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>56583</t>
+          <t>57105</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>86354</t>
+          <t>87454</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -10907,12 +10907,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>16,92%</t>
+          <t>17,08%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>25,83%</t>
+          <t>26,16%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -10927,12 +10927,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>103580</t>
+          <t>104405</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>139964</t>
+          <t>142325</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -10942,12 +10942,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>27,42%</t>
+          <t>27,64%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>37,05%</t>
+          <t>37,68%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -10962,12 +10962,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>169160</t>
+          <t>169699</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>218129</t>
+          <t>217854</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -10977,12 +10977,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>23,76%</t>
+          <t>23,83%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>30,63%</t>
+          <t>30,59%</t>
         </is>
       </c>
     </row>
@@ -11005,12 +11005,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>22536</t>
+          <t>22829</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>42869</t>
+          <t>43739</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -11020,12 +11020,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>6,74%</t>
+          <t>6,83%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>12,82%</t>
+          <t>13,08%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -11040,12 +11040,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>41554</t>
+          <t>41341</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>68609</t>
+          <t>67939</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -11055,12 +11055,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>11,0%</t>
+          <t>10,94%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>18,16%</t>
+          <t>17,98%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -11075,12 +11075,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>70760</t>
+          <t>70889</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>104622</t>
+          <t>105514</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -11090,12 +11090,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>9,94%</t>
+          <t>9,96%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>14,69%</t>
+          <t>14,82%</t>
         </is>
       </c>
     </row>
@@ -11235,12 +11235,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>101263</t>
+          <t>98820</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>126987</t>
+          <t>128812</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -11250,12 +11250,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>39,4%</t>
+          <t>38,45%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>49,41%</t>
+          <t>50,12%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -11270,12 +11270,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>98322</t>
+          <t>101086</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>142371</t>
+          <t>141584</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -11285,12 +11285,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>24,57%</t>
+          <t>25,26%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>35,58%</t>
+          <t>35,38%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -11305,12 +11305,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>206992</t>
+          <t>206585</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>259318</t>
+          <t>259675</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -11320,12 +11320,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>31,5%</t>
+          <t>31,44%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>39,46%</t>
+          <t>39,51%</t>
         </is>
       </c>
     </row>
@@ -11348,12 +11348,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>80668</t>
+          <t>80999</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>107653</t>
+          <t>108754</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -11363,12 +11363,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>31,39%</t>
+          <t>31,52%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>41,89%</t>
+          <t>42,32%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -11383,12 +11383,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>128531</t>
+          <t>128280</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>170159</t>
+          <t>171796</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -11398,12 +11398,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>32,12%</t>
+          <t>32,06%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>42,52%</t>
+          <t>42,93%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -11418,12 +11418,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>221784</t>
+          <t>221357</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>272078</t>
+          <t>270654</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -11433,12 +11433,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>33,75%</t>
+          <t>33,68%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>41,4%</t>
+          <t>41,18%</t>
         </is>
       </c>
     </row>
@@ -11461,12 +11461,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>38577</t>
+          <t>38491</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>61772</t>
+          <t>61971</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -11476,12 +11476,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>15,01%</t>
+          <t>14,98%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>24,04%</t>
+          <t>24,11%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -11496,12 +11496,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>110914</t>
+          <t>109875</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>153707</t>
+          <t>152775</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -11511,12 +11511,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>27,72%</t>
+          <t>27,46%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>38,41%</t>
+          <t>38,18%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -11531,12 +11531,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>155200</t>
+          <t>154232</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>203538</t>
+          <t>203502</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -11546,7 +11546,7 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>23,62%</t>
+          <t>23,47%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
@@ -11691,12 +11691,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>2877214</t>
+          <t>2882276</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>2961766</t>
+          <t>2961057</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -11706,12 +11706,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>84,76%</t>
+          <t>84,91%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>87,26%</t>
+          <t>87,23%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -11726,12 +11726,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>2690030</t>
+          <t>2686179</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>2792964</t>
+          <t>2794762</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -11741,12 +11741,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>75,89%</t>
+          <t>75,78%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>78,8%</t>
+          <t>78,85%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -11761,12 +11761,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>5599692</t>
+          <t>5596147</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>5733595</t>
+          <t>5738098</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -11776,12 +11776,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>80,7%</t>
+          <t>80,65%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>82,63%</t>
+          <t>82,69%</t>
         </is>
       </c>
     </row>
@@ -11804,12 +11804,12 @@
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>289822</t>
+          <t>291365</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>361242</t>
+          <t>362002</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
@@ -11819,12 +11819,12 @@
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>8,54%</t>
+          <t>8,58%</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>10,64%</t>
+          <t>10,66%</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
@@ -11839,12 +11839,12 @@
       </c>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>458988</t>
+          <t>461591</t>
         </is>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>543207</t>
+          <t>547083</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
@@ -11854,12 +11854,12 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>12,95%</t>
+          <t>13,02%</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
         <is>
-          <t>15,33%</t>
+          <t>15,43%</t>
         </is>
       </c>
       <c r="Q33" s="2" t="inlineStr">
@@ -11874,12 +11874,12 @@
       </c>
       <c r="S33" s="2" t="inlineStr">
         <is>
-          <t>768341</t>
+          <t>768934</t>
         </is>
       </c>
       <c r="T33" s="2" t="inlineStr">
         <is>
-          <t>881772</t>
+          <t>879884</t>
         </is>
       </c>
       <c r="U33" s="2" t="inlineStr">
@@ -11889,12 +11889,12 @@
       </c>
       <c r="V33" s="2" t="inlineStr">
         <is>
-          <t>11,07%</t>
+          <t>11,08%</t>
         </is>
       </c>
       <c r="W33" s="2" t="inlineStr">
         <is>
-          <t>12,71%</t>
+          <t>12,68%</t>
         </is>
       </c>
     </row>
@@ -11917,12 +11917,12 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>123579</t>
+          <t>124676</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>171287</t>
+          <t>170693</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -11932,12 +11932,12 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>3,64%</t>
+          <t>3,67%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>5,05%</t>
+          <t>5,03%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -11952,12 +11952,12 @@
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>266832</t>
+          <t>263048</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>336917</t>
+          <t>337618</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -11967,12 +11967,12 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>7,53%</t>
+          <t>7,42%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>9,51%</t>
+          <t>9,53%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -11987,12 +11987,12 @@
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>404517</t>
+          <t>401607</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>486863</t>
+          <t>493682</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -12002,12 +12002,12 @@
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>5,83%</t>
+          <t>5,79%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>7,02%</t>
+          <t>7,11%</t>
         </is>
       </c>
     </row>
@@ -12377,32 +12377,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>392520</t>
+          <t>401049</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>376978</t>
+          <t>387657</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>398267</t>
+          <t>406314</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>98,13%</t>
+          <t>98,35%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>94,25%</t>
+          <t>95,06%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>99,57%</t>
+          <t>99,64%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -12412,32 +12412,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>310263</t>
+          <t>356932</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>303718</t>
+          <t>347342</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>313037</t>
+          <t>361243</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>99,06%</t>
+          <t>98,46%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>96,97%</t>
+          <t>95,82%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>99,95%</t>
+          <t>99,65%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -12447,32 +12447,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>702783</t>
+          <t>757981</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>683573</t>
+          <t>743540</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>709231</t>
+          <t>765681</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>98,54%</t>
+          <t>98,4%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>95,85%</t>
+          <t>96,53%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>99,45%</t>
+          <t>99,4%</t>
         </is>
       </c>
     </row>
@@ -12490,32 +12490,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>7467</t>
+          <t>6744</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>1720</t>
+          <t>1479</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>23009</t>
+          <t>20136</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>1,87%</t>
+          <t>1,65%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0,43%</t>
+          <t>0,36%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>5,75%</t>
+          <t>4,94%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -12525,7 +12525,7 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>1153</t>
+          <t>1324</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
@@ -12535,7 +12535,7 @@
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>6500</t>
+          <t>8107</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -12550,7 +12550,7 @@
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>2,08%</t>
+          <t>2,24%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -12560,32 +12560,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>8620</t>
+          <t>8068</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1933</t>
+          <t>1871</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>26884</t>
+          <t>20750</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>1,21%</t>
+          <t>1,05%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>0,27%</t>
+          <t>0,24%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>3,77%</t>
+          <t>2,69%</t>
         </is>
       </c>
     </row>
@@ -12638,7 +12638,7 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>1784</t>
+          <t>4256</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
@@ -12648,12 +12648,12 @@
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>9285</t>
+          <t>14931</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>0,57%</t>
+          <t>1,17%</t>
         </is>
       </c>
       <c r="O6" s="2" t="inlineStr">
@@ -12663,7 +12663,7 @@
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>2,96%</t>
+          <t>4,12%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -12673,7 +12673,7 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>1784</t>
+          <t>4256</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
@@ -12683,12 +12683,12 @@
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>9861</t>
+          <t>14759</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
         <is>
-          <t>0,25%</t>
+          <t>0,55%</t>
         </is>
       </c>
       <c r="V6" s="2" t="inlineStr">
@@ -12698,7 +12698,7 @@
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>1,38%</t>
+          <t>1,92%</t>
         </is>
       </c>
     </row>
@@ -12716,17 +12716,17 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>399987</t>
+          <t>407793</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>399987</t>
+          <t>407793</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>399987</t>
+          <t>407793</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -12751,17 +12751,17 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>313200</t>
+          <t>362512</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>313200</t>
+          <t>362512</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>313200</t>
+          <t>362512</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -12786,17 +12786,17 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>713187</t>
+          <t>770305</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>713187</t>
+          <t>770305</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>713187</t>
+          <t>770305</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -12833,32 +12833,32 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>401199</t>
+          <t>452660</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>386083</t>
+          <t>435917</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>410311</t>
+          <t>462736</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>94,72%</t>
+          <t>94,92%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>91,15%</t>
+          <t>91,41%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>96,88%</t>
+          <t>97,03%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -12868,32 +12868,32 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>506417</t>
+          <t>495172</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>499534</t>
+          <t>488317</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>510216</t>
+          <t>499127</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>98,89%</t>
+          <t>98,69%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>97,55%</t>
+          <t>97,33%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>99,63%</t>
+          <t>99,48%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -12903,32 +12903,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>907616</t>
+          <t>947832</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>891223</t>
+          <t>930343</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>918988</t>
+          <t>959139</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>97,0%</t>
+          <t>96,85%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>95,25%</t>
+          <t>95,07%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>98,22%</t>
+          <t>98,01%</t>
         </is>
       </c>
     </row>
@@ -12946,32 +12946,32 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>17459</t>
+          <t>17390</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>8994</t>
+          <t>8712</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>31980</t>
+          <t>33306</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>4,12%</t>
+          <t>3,65%</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>2,12%</t>
+          <t>1,83%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>7,55%</t>
+          <t>6,98%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -12981,32 +12981,32 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>4762</t>
+          <t>5614</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>1577</t>
+          <t>2154</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>11645</t>
+          <t>11984</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>0,93%</t>
+          <t>1,12%</t>
         </is>
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>0,31%</t>
+          <t>0,43%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>2,27%</t>
+          <t>2,39%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -13016,22 +13016,22 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>22221</t>
+          <t>23005</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>12500</t>
+          <t>13138</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>38229</t>
+          <t>39917</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
         <is>
-          <t>2,37%</t>
+          <t>2,35%</t>
         </is>
       </c>
       <c r="V9" s="2" t="inlineStr">
@@ -13041,7 +13041,7 @@
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>4,09%</t>
+          <t>4,08%</t>
         </is>
       </c>
     </row>
@@ -13059,32 +13059,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>4889</t>
+          <t>6840</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>1449</t>
+          <t>2510</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>11998</t>
+          <t>15045</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>1,15%</t>
+          <t>1,43%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>0,34%</t>
+          <t>0,53%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>2,83%</t>
+          <t>3,15%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -13094,7 +13094,7 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>914</t>
+          <t>947</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
@@ -13104,12 +13104,12 @@
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>5367</t>
+          <t>5376</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>0,18%</t>
+          <t>0,19%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
@@ -13119,7 +13119,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>1,05%</t>
+          <t>1,07%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -13129,32 +13129,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>5803</t>
+          <t>7786</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>2111</t>
+          <t>3133</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>13039</t>
+          <t>16003</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>0,62%</t>
+          <t>0,8%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>0,23%</t>
+          <t>0,32%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>1,39%</t>
+          <t>1,64%</t>
         </is>
       </c>
     </row>
@@ -13172,17 +13172,17 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>423547</t>
+          <t>476890</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>423547</t>
+          <t>476890</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>423547</t>
+          <t>476890</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -13207,17 +13207,17 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>512093</t>
+          <t>501733</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>512093</t>
+          <t>501733</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>512093</t>
+          <t>501733</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -13242,17 +13242,17 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>935640</t>
+          <t>978623</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>935640</t>
+          <t>978623</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>935640</t>
+          <t>978623</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -13289,32 +13289,32 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>505604</t>
+          <t>589864</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>492720</t>
+          <t>576402</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>515241</t>
+          <t>600160</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>94,27%</t>
+          <t>95,01%</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>91,87%</t>
+          <t>92,84%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>96,07%</t>
+          <t>96,67%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -13324,32 +13324,32 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>549203</t>
+          <t>573405</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>537117</t>
+          <t>561052</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>561799</t>
+          <t>583226</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>92,86%</t>
+          <t>92,11%</t>
         </is>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>90,81%</t>
+          <t>90,12%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>94,99%</t>
+          <t>93,68%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -13359,32 +13359,32 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>1054806</t>
+          <t>1163269</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>1038036</t>
+          <t>1144247</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>1069839</t>
+          <t>1177974</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
         <is>
-          <t>93,53%</t>
+          <t>93,56%</t>
         </is>
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>92,04%</t>
+          <t>92,03%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>94,86%</t>
+          <t>94,74%</t>
         </is>
       </c>
     </row>
@@ -13402,32 +13402,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>27074</t>
+          <t>27163</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>18100</t>
+          <t>18054</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>38987</t>
+          <t>40355</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>5,05%</t>
+          <t>4,38%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>3,37%</t>
+          <t>2,91%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>7,27%</t>
+          <t>6,5%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -13437,32 +13437,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>31439</t>
+          <t>37335</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>21472</t>
+          <t>27481</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>42687</t>
+          <t>48410</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>5,32%</t>
+          <t>6,0%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>3,63%</t>
+          <t>4,41%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>7,22%</t>
+          <t>7,78%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -13472,17 +13472,17 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>58513</t>
+          <t>64498</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>45617</t>
+          <t>50491</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>74425</t>
+          <t>80435</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -13492,12 +13492,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>4,04%</t>
+          <t>4,06%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>6,6%</t>
+          <t>6,47%</t>
         </is>
       </c>
     </row>
@@ -13515,32 +13515,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>3660</t>
+          <t>3810</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>1053</t>
+          <t>1139</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>10584</t>
+          <t>11286</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>0,68%</t>
+          <t>0,61%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>0,2%</t>
+          <t>0,18%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>1,97%</t>
+          <t>1,82%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -13550,32 +13550,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>10815</t>
+          <t>11816</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>5921</t>
+          <t>6994</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>17432</t>
+          <t>18022</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>1,83%</t>
+          <t>1,9%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>1,0%</t>
+          <t>1,12%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>2,95%</t>
+          <t>2,89%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -13585,32 +13585,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>14475</t>
+          <t>15626</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>8933</t>
+          <t>9540</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>22432</t>
+          <t>25010</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>1,28%</t>
+          <t>1,26%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>0,79%</t>
+          <t>0,77%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>1,99%</t>
+          <t>2,01%</t>
         </is>
       </c>
     </row>
@@ -13628,17 +13628,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>536338</t>
+          <t>620837</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>536338</t>
+          <t>620837</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>536338</t>
+          <t>620837</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -13663,17 +13663,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>591457</t>
+          <t>622556</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>591457</t>
+          <t>622556</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>591457</t>
+          <t>622556</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -13698,17 +13698,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>1127795</t>
+          <t>1243393</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>1127795</t>
+          <t>1243393</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>1127795</t>
+          <t>1243393</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -13745,32 +13745,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>570608</t>
+          <t>618835</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>236738</t>
+          <t>597402</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>794662</t>
+          <t>634676</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>64,27%</t>
+          <t>88,33%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>26,67%</t>
+          <t>85,27%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>89,51%</t>
+          <t>90,59%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -13780,32 +13780,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>614944</t>
+          <t>635016</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>595539</t>
+          <t>619568</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>632476</t>
+          <t>648860</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>86,26%</t>
+          <t>86,18%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>83,54%</t>
+          <t>84,08%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>88,72%</t>
+          <t>88,05%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -13815,32 +13815,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>1185552</t>
+          <t>1253851</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>782729</t>
+          <t>1228639</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>1407067</t>
+          <t>1276054</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>74,07%</t>
+          <t>87,22%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>48,9%</t>
+          <t>85,47%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>87,91%</t>
+          <t>88,77%</t>
         </is>
       </c>
     </row>
@@ -13858,32 +13858,32 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>291545</t>
+          <t>52253</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>59840</t>
+          <t>39012</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>639445</t>
+          <t>69507</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>32,84%</t>
+          <t>7,46%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>6,74%</t>
+          <t>5,57%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>72,03%</t>
+          <t>9,92%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -13893,32 +13893,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>75648</t>
+          <t>78311</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>61759</t>
+          <t>65796</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>95444</t>
+          <t>92304</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>10,61%</t>
+          <t>10,63%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>8,66%</t>
+          <t>8,93%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>13,39%</t>
+          <t>12,53%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -13928,32 +13928,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>367192</t>
+          <t>130565</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>137876</t>
+          <t>111217</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>779048</t>
+          <t>151407</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>22,94%</t>
+          <t>9,08%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>8,61%</t>
+          <t>7,74%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>48,67%</t>
+          <t>10,53%</t>
         </is>
       </c>
     </row>
@@ -13971,32 +13971,32 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>25634</t>
+          <t>29529</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>10386</t>
+          <t>18784</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>43002</t>
+          <t>43290</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>2,89%</t>
+          <t>4,21%</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>1,17%</t>
+          <t>2,68%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>4,84%</t>
+          <t>6,18%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -14006,32 +14006,32 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>22289</t>
+          <t>23559</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>15219</t>
+          <t>17116</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>29699</t>
+          <t>31796</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>3,13%</t>
+          <t>3,2%</t>
         </is>
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>2,13%</t>
+          <t>2,32%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>4,17%</t>
+          <t>4,31%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -14041,32 +14041,32 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>47923</t>
+          <t>53088</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>28946</t>
+          <t>40606</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>66022</t>
+          <t>68967</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
         <is>
-          <t>2,99%</t>
+          <t>3,69%</t>
         </is>
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>1,81%</t>
+          <t>2,82%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>4,12%</t>
+          <t>4,8%</t>
         </is>
       </c>
     </row>
@@ -14084,17 +14084,17 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>887786</t>
+          <t>700617</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>887786</t>
+          <t>700617</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>887786</t>
+          <t>700617</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -14119,17 +14119,17 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>712881</t>
+          <t>736886</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>712881</t>
+          <t>736886</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>712881</t>
+          <t>736886</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -14154,17 +14154,17 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>1600667</t>
+          <t>1437504</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>1600667</t>
+          <t>1437504</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>1600667</t>
+          <t>1437504</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -14201,32 +14201,32 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>448002</t>
+          <t>489665</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>429248</t>
+          <t>467891</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>465511</t>
+          <t>506485</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>79,82%</t>
+          <t>80,36%</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>76,48%</t>
+          <t>76,79%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>82,94%</t>
+          <t>83,12%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -14236,32 +14236,32 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>411359</t>
+          <t>455576</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>396860</t>
+          <t>437908</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>427095</t>
+          <t>471042</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>75,08%</t>
+          <t>74,82%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>72,43%</t>
+          <t>71,92%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>77,95%</t>
+          <t>77,37%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -14271,32 +14271,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>859360</t>
+          <t>945242</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>833143</t>
+          <t>917467</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>881532</t>
+          <t>969900</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>77,48%</t>
+          <t>77,59%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>75,12%</t>
+          <t>75,31%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>79,48%</t>
+          <t>79,62%</t>
         </is>
       </c>
     </row>
@@ -14314,32 +14314,32 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>83762</t>
+          <t>88511</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>68705</t>
+          <t>74048</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>101358</t>
+          <t>108597</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>14,92%</t>
+          <t>14,53%</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>12,24%</t>
+          <t>12,15%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>18,06%</t>
+          <t>17,82%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -14349,32 +14349,32 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>99540</t>
+          <t>110352</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>87177</t>
+          <t>95820</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>113509</t>
+          <t>124408</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>18,17%</t>
+          <t>18,12%</t>
         </is>
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>15,91%</t>
+          <t>15,74%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>20,72%</t>
+          <t>20,43%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -14384,32 +14384,32 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>183302</t>
+          <t>198863</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>161932</t>
+          <t>176782</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>206491</t>
+          <t>223455</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
         <is>
-          <t>16,53%</t>
+          <t>16,32%</t>
         </is>
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>14,6%</t>
+          <t>14,51%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>18,62%</t>
+          <t>18,34%</t>
         </is>
       </c>
     </row>
@@ -14427,32 +14427,32 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>29471</t>
+          <t>31170</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>21120</t>
+          <t>21519</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>40231</t>
+          <t>42819</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>5,25%</t>
+          <t>5,12%</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>3,76%</t>
+          <t>3,53%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>7,17%</t>
+          <t>7,03%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -14462,32 +14462,32 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>37006</t>
+          <t>42927</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>28927</t>
+          <t>33696</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>46595</t>
+          <t>52692</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>6,75%</t>
+          <t>7,05%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>5,28%</t>
+          <t>5,53%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>8,5%</t>
+          <t>8,65%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -14497,32 +14497,32 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>66477</t>
+          <t>74097</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>54763</t>
+          <t>61239</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>80695</t>
+          <t>90335</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>5,99%</t>
+          <t>6,08%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>4,94%</t>
+          <t>5,03%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>7,28%</t>
+          <t>7,42%</t>
         </is>
       </c>
     </row>
@@ -14540,17 +14540,17 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>561234</t>
+          <t>609346</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>561234</t>
+          <t>609346</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>561234</t>
+          <t>609346</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -14575,17 +14575,17 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>547905</t>
+          <t>608855</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>547905</t>
+          <t>608855</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>547905</t>
+          <t>608855</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -14610,17 +14610,17 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>1109139</t>
+          <t>1218202</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>1109139</t>
+          <t>1218202</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>1109139</t>
+          <t>1218202</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -14657,32 +14657,32 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>283264</t>
+          <t>314832</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>270971</t>
+          <t>301313</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>295473</t>
+          <t>328821</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>76,94%</t>
+          <t>77,34%</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>73,6%</t>
+          <t>74,02%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>80,26%</t>
+          <t>80,78%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -14692,32 +14692,32 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>452843</t>
+          <t>266724</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>368306</t>
+          <t>252314</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>540187</t>
+          <t>282562</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>74,44%</t>
+          <t>60,73%</t>
         </is>
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>60,54%</t>
+          <t>57,45%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>88,79%</t>
+          <t>64,34%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -14727,32 +14727,32 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>736107</t>
+          <t>581555</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>664803</t>
+          <t>561272</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>848811</t>
+          <t>603369</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
         <is>
-          <t>75,38%</t>
+          <t>68,72%</t>
         </is>
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>68,08%</t>
+          <t>66,32%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>86,92%</t>
+          <t>71,3%</t>
         </is>
       </c>
     </row>
@@ -14770,32 +14770,32 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>58632</t>
+          <t>64223</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>48534</t>
+          <t>52692</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>69950</t>
+          <t>76490</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>15,93%</t>
+          <t>15,78%</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>13,18%</t>
+          <t>12,94%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>19,0%</t>
+          <t>18,79%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -14805,32 +14805,32 @@
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>118335</t>
+          <t>129877</t>
         </is>
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>51989</t>
+          <t>115863</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>184114</t>
+          <t>144350</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t>19,45%</t>
+          <t>29,57%</t>
         </is>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>8,55%</t>
+          <t>26,38%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>30,26%</t>
+          <t>32,87%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -14840,32 +14840,32 @@
       </c>
       <c r="R25" s="2" t="inlineStr">
         <is>
-          <t>176967</t>
+          <t>194099</t>
         </is>
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>92266</t>
+          <t>174819</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>230930</t>
+          <t>212549</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
         <is>
-          <t>18,12%</t>
+          <t>22,94%</t>
         </is>
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>9,45%</t>
+          <t>20,66%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>23,65%</t>
+          <t>25,12%</t>
         </is>
       </c>
     </row>
@@ -14883,32 +14883,32 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>26268</t>
+          <t>28025</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>18921</t>
+          <t>20173</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>35573</t>
+          <t>38957</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>7,13%</t>
+          <t>6,88%</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>5,14%</t>
+          <t>4,96%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>9,66%</t>
+          <t>9,57%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -14918,32 +14918,32 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>37191</t>
+          <t>42566</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>16154</t>
+          <t>33277</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>60478</t>
+          <t>52714</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>6,11%</t>
+          <t>9,69%</t>
         </is>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>2,66%</t>
+          <t>7,58%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>9,94%</t>
+          <t>12,0%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -14953,32 +14953,32 @@
       </c>
       <c r="R26" s="2" t="inlineStr">
         <is>
-          <t>63459</t>
+          <t>70591</t>
         </is>
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>32354</t>
+          <t>59551</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>86478</t>
+          <t>84366</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
         <is>
-          <t>6,5%</t>
+          <t>8,34%</t>
         </is>
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>3,31%</t>
+          <t>7,04%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>8,86%</t>
+          <t>9,97%</t>
         </is>
       </c>
     </row>
@@ -14996,17 +14996,17 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>368165</t>
+          <t>407080</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>368165</t>
+          <t>407080</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>368165</t>
+          <t>407080</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -15031,17 +15031,17 @@
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>608368</t>
+          <t>439166</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>608368</t>
+          <t>439166</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>608368</t>
+          <t>439166</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -15066,17 +15066,17 @@
       </c>
       <c r="R27" s="2" t="inlineStr">
         <is>
-          <t>976533</t>
+          <t>846246</t>
         </is>
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>976533</t>
+          <t>846246</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>976533</t>
+          <t>846246</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -15113,32 +15113,32 @@
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>141812</t>
+          <t>155367</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>128419</t>
+          <t>141503</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>156058</t>
+          <t>170702</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t>50,15%</t>
+          <t>50,09%</t>
         </is>
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>45,42%</t>
+          <t>45,62%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>55,19%</t>
+          <t>55,03%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -15148,32 +15148,32 @@
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>110841</t>
+          <t>121244</t>
         </is>
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>99255</t>
+          <t>108736</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>123997</t>
+          <t>136777</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
         <is>
-          <t>26,03%</t>
+          <t>26,1%</t>
         </is>
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>23,31%</t>
+          <t>23,4%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>29,12%</t>
+          <t>29,44%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -15183,32 +15183,32 @@
       </c>
       <c r="R28" s="2" t="inlineStr">
         <is>
-          <t>252653</t>
+          <t>276611</t>
         </is>
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>234670</t>
+          <t>257444</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>271568</t>
+          <t>298741</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
         <is>
-          <t>35,66%</t>
+          <t>35,7%</t>
         </is>
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>33,12%</t>
+          <t>33,23%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>38,33%</t>
+          <t>38,56%</t>
         </is>
       </c>
     </row>
@@ -15226,32 +15226,32 @@
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>89556</t>
+          <t>99041</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>76653</t>
+          <t>86333</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>102686</t>
+          <t>112772</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>31,67%</t>
+          <t>31,93%</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>27,11%</t>
+          <t>27,83%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>36,32%</t>
+          <t>36,35%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -15261,32 +15261,32 @@
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>158144</t>
+          <t>169935</t>
         </is>
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>142197</t>
+          <t>154602</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>170520</t>
+          <t>184194</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
-          <t>37,14%</t>
+          <t>36,58%</t>
         </is>
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>33,39%</t>
+          <t>33,28%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>40,04%</t>
+          <t>39,64%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -15296,32 +15296,32 @@
       </c>
       <c r="R29" s="2" t="inlineStr">
         <is>
-          <t>247701</t>
+          <t>268977</t>
         </is>
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>228622</t>
+          <t>249073</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>265839</t>
+          <t>289488</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
         <is>
-          <t>34,96%</t>
+          <t>34,72%</t>
         </is>
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>32,26%</t>
+          <t>32,15%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>37,52%</t>
+          <t>37,36%</t>
         </is>
       </c>
     </row>
@@ -15339,32 +15339,32 @@
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>51391</t>
+          <t>55789</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>42140</t>
+          <t>45568</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>62195</t>
+          <t>68635</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>18,17%</t>
+          <t>17,99%</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>14,9%</t>
+          <t>14,69%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>22,0%</t>
+          <t>22,13%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -15374,32 +15374,32 @@
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>156846</t>
+          <t>173430</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>143568</t>
+          <t>157788</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>171465</t>
+          <t>189266</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
         <is>
-          <t>36,83%</t>
+          <t>37,33%</t>
         </is>
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>33,71%</t>
+          <t>33,96%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>40,27%</t>
+          <t>40,74%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -15409,32 +15409,32 @@
       </c>
       <c r="R30" s="2" t="inlineStr">
         <is>
-          <t>208236</t>
+          <t>229219</t>
         </is>
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>191131</t>
+          <t>211733</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>227631</t>
+          <t>250739</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
         <is>
-          <t>29,39%</t>
+          <t>29,58%</t>
         </is>
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>26,97%</t>
+          <t>27,33%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>32,12%</t>
+          <t>32,36%</t>
         </is>
       </c>
     </row>
@@ -15452,17 +15452,17 @@
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>282759</t>
+          <t>310198</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>282759</t>
+          <t>310198</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>282759</t>
+          <t>310198</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -15487,17 +15487,17 @@
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>425831</t>
+          <t>464609</t>
         </is>
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>425831</t>
+          <t>464609</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>425831</t>
+          <t>464609</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -15522,17 +15522,17 @@
       </c>
       <c r="R31" s="2" t="inlineStr">
         <is>
-          <t>708590</t>
+          <t>774807</t>
         </is>
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>708590</t>
+          <t>774807</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>708590</t>
+          <t>774807</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -15569,32 +15569,32 @@
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t>2743009</t>
+          <t>3022273</t>
         </is>
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>2152743</t>
+          <t>2978377</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>2967652</t>
+          <t>3062900</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
         <is>
-          <t>79,28%</t>
+          <t>85,55%</t>
         </is>
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>62,22%</t>
+          <t>84,31%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>85,77%</t>
+          <t>86,7%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -15604,32 +15604,32 @@
       </c>
       <c r="K32" s="2" t="inlineStr">
         <is>
-          <t>2955870</t>
+          <t>2904068</t>
         </is>
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>2883793</t>
+          <t>2862764</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>3098624</t>
+          <t>2943458</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
         <is>
-          <t>79,64%</t>
+          <t>77,73%</t>
         </is>
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>77,69%</t>
+          <t>76,62%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>83,48%</t>
+          <t>78,78%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -15639,32 +15639,32 @@
       </c>
       <c r="R32" s="2" t="inlineStr">
         <is>
-          <t>5698879</t>
+          <t>5926342</t>
         </is>
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>5036625</t>
+          <t>5868583</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>5942376</t>
+          <t>5986143</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
         <is>
-          <t>79,47%</t>
+          <t>81,53%</t>
         </is>
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>70,23%</t>
+          <t>80,73%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>82,86%</t>
+          <t>82,35%</t>
         </is>
       </c>
     </row>
@@ -15682,32 +15682,32 @@
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>575495</t>
+          <t>355326</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>342667</t>
+          <t>323363</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>1199362</t>
+          <t>394305</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>16,63%</t>
+          <t>10,06%</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>9,9%</t>
+          <t>9,15%</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>34,67%</t>
+          <t>11,16%</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
@@ -15717,32 +15717,32 @@
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>489021</t>
+          <t>532748</t>
         </is>
       </c>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>392132</t>
+          <t>501044</t>
         </is>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>538496</t>
+          <t>565516</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
         <is>
-          <t>13,17%</t>
+          <t>14,26%</t>
         </is>
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>10,56%</t>
+          <t>13,41%</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
         <is>
-          <t>14,51%</t>
+          <t>15,14%</t>
         </is>
       </c>
       <c r="Q33" s="2" t="inlineStr">
@@ -15752,32 +15752,32 @@
       </c>
       <c r="R33" s="2" t="inlineStr">
         <is>
-          <t>1064516</t>
+          <t>888074</t>
         </is>
       </c>
       <c r="S33" s="2" t="inlineStr">
         <is>
-          <t>821386</t>
+          <t>839471</t>
         </is>
       </c>
       <c r="T33" s="2" t="inlineStr">
         <is>
-          <t>1734167</t>
+          <t>940931</t>
         </is>
       </c>
       <c r="U33" s="2" t="inlineStr">
         <is>
-          <t>14,84%</t>
+          <t>12,22%</t>
         </is>
       </c>
       <c r="V33" s="2" t="inlineStr">
         <is>
-          <t>11,45%</t>
+          <t>11,55%</t>
         </is>
       </c>
       <c r="W33" s="2" t="inlineStr">
         <is>
-          <t>24,18%</t>
+          <t>12,94%</t>
         </is>
       </c>
     </row>
@@ -15795,32 +15795,32 @@
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
-          <t>141313</t>
+          <t>155163</t>
         </is>
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>107734</t>
+          <t>134102</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>165951</t>
+          <t>180147</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
         <is>
-          <t>4,08%</t>
+          <t>4,39%</t>
         </is>
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>3,11%</t>
+          <t>3,8%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>4,8%</t>
+          <t>5,1%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -15830,32 +15830,32 @@
       </c>
       <c r="K34" s="2" t="inlineStr">
         <is>
-          <t>266844</t>
+          <t>299501</t>
         </is>
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>220567</t>
+          <t>275315</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>298997</t>
+          <t>324529</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
         <is>
-          <t>7,19%</t>
+          <t>8,02%</t>
         </is>
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>5,94%</t>
+          <t>7,37%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>8,06%</t>
+          <t>8,69%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -15865,32 +15865,32 @@
       </c>
       <c r="R34" s="2" t="inlineStr">
         <is>
-          <t>408157</t>
+          <t>454664</t>
         </is>
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>353317</t>
+          <t>422844</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>451446</t>
+          <t>493072</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
         <is>
-          <t>5,69%</t>
+          <t>6,25%</t>
         </is>
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>4,93%</t>
+          <t>5,82%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>6,29%</t>
+          <t>6,78%</t>
         </is>
       </c>
     </row>
@@ -15908,17 +15908,17 @@
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>3459817</t>
+          <t>3532762</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>3459817</t>
+          <t>3532762</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>3459817</t>
+          <t>3532762</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
@@ -15943,17 +15943,17 @@
       </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t>3711735</t>
+          <t>3736318</t>
         </is>
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>3711735</t>
+          <t>3736318</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>3711735</t>
+          <t>3736318</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
@@ -15978,17 +15978,17 @@
       </c>
       <c r="R35" s="2" t="inlineStr">
         <is>
-          <t>7171552</t>
+          <t>7269080</t>
         </is>
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t>7171552</t>
+          <t>7269080</t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>7171552</t>
+          <t>7269080</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
